--- a/Sheets/Salaries.xlsx
+++ b/Sheets/Salaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\SalariesSummary\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30106874-9521-4624-B0C1-793E4C3E8285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C068724F-830D-467D-B7E0-158BC0E48612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,9 @@
     <sheet name="Pay Clip (AR)" sheetId="4" r:id="rId4"/>
     <sheet name="Pay Clip (EN)" sheetId="5" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="156">
   <si>
     <t>ديسمبر 2025</t>
   </si>
@@ -480,6 +483,36 @@
   <si>
     <t>NET</t>
   </si>
+  <si>
+    <t>إضافات غير مباشرة / In direct additions</t>
+  </si>
+  <si>
+    <t>إضافات مباشرة / Direct Additions</t>
+  </si>
+  <si>
+    <t>علاوات / Bouns</t>
+  </si>
+  <si>
+    <t>خصومات / Deductions</t>
+  </si>
+  <si>
+    <t>الإجمالي قبل الخصم
+GROSS</t>
+  </si>
+  <si>
+    <t>الصافى بعد الخصم
+ أو الزيادة
+NET</t>
+  </si>
+  <si>
+    <t>طريقة الدفع</t>
+  </si>
+  <si>
+    <t>رقم الحساب</t>
+  </si>
+  <si>
+    <t>تحويل/شيك</t>
+  </si>
 </sst>
 </file>
 
@@ -817,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -972,6 +1005,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1198,6 +1234,2141 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="مرتبات"/>
+      <sheetName val="اضافات"/>
+      <sheetName val="خصومات"/>
+      <sheetName val="Pay Clip (AR)"/>
+      <sheetName val="Pay Clip (EN)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="4">
+          <cell r="F4">
+            <v>0</v>
+          </cell>
+          <cell r="M4">
+            <v>0</v>
+          </cell>
+          <cell r="N4">
+            <v>0</v>
+          </cell>
+          <cell r="O4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5">
+            <v>0</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="N5">
+            <v>0</v>
+          </cell>
+          <cell r="O5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>0</v>
+          </cell>
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+          <cell r="N6">
+            <v>0</v>
+          </cell>
+          <cell r="O6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="F7">
+            <v>0</v>
+          </cell>
+          <cell r="M7">
+            <v>0</v>
+          </cell>
+          <cell r="N7">
+            <v>0</v>
+          </cell>
+          <cell r="O7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="F8">
+            <v>0</v>
+          </cell>
+          <cell r="M8">
+            <v>0</v>
+          </cell>
+          <cell r="N8">
+            <v>0</v>
+          </cell>
+          <cell r="O8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="F9">
+            <v>0</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+          <cell r="N9">
+            <v>0</v>
+          </cell>
+          <cell r="O9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="F10">
+            <v>0</v>
+          </cell>
+          <cell r="M10">
+            <v>0</v>
+          </cell>
+          <cell r="N10">
+            <v>0</v>
+          </cell>
+          <cell r="O10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11">
+            <v>0</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+          <cell r="N11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="F12">
+            <v>0</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
+            <v>0</v>
+          </cell>
+          <cell r="O12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="F13">
+            <v>0</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
+            <v>0</v>
+          </cell>
+          <cell r="O13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="F14">
+            <v>0</v>
+          </cell>
+          <cell r="M14">
+            <v>0</v>
+          </cell>
+          <cell r="N14">
+            <v>0</v>
+          </cell>
+          <cell r="O14">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="F15">
+            <v>0</v>
+          </cell>
+          <cell r="M15">
+            <v>0</v>
+          </cell>
+          <cell r="N15">
+            <v>0</v>
+          </cell>
+          <cell r="O15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="F16">
+            <v>0</v>
+          </cell>
+          <cell r="M16">
+            <v>0</v>
+          </cell>
+          <cell r="N16">
+            <v>0</v>
+          </cell>
+          <cell r="O16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="F17">
+            <v>0</v>
+          </cell>
+          <cell r="M17">
+            <v>0</v>
+          </cell>
+          <cell r="N17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="F19">
+            <v>0</v>
+          </cell>
+          <cell r="M19">
+            <v>0</v>
+          </cell>
+          <cell r="N19">
+            <v>0</v>
+          </cell>
+          <cell r="O19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="F20">
+            <v>0</v>
+          </cell>
+          <cell r="M20">
+            <v>0</v>
+          </cell>
+          <cell r="N20">
+            <v>0</v>
+          </cell>
+          <cell r="O20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="F21">
+            <v>0</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+          <cell r="N21">
+            <v>0</v>
+          </cell>
+          <cell r="O21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="F22">
+            <v>0</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+          <cell r="N22">
+            <v>0</v>
+          </cell>
+          <cell r="O22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="F23">
+            <v>0</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+          <cell r="N23">
+            <v>0</v>
+          </cell>
+          <cell r="O23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="F24">
+            <v>0</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+          <cell r="N24">
+            <v>0</v>
+          </cell>
+          <cell r="O24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="F25">
+            <v>0</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+          <cell r="N25">
+            <v>0</v>
+          </cell>
+          <cell r="O25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="F26">
+            <v>0</v>
+          </cell>
+          <cell r="M26">
+            <v>0</v>
+          </cell>
+          <cell r="N26">
+            <v>0</v>
+          </cell>
+          <cell r="O26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="F27">
+            <v>0</v>
+          </cell>
+          <cell r="M27">
+            <v>0</v>
+          </cell>
+          <cell r="N27">
+            <v>0</v>
+          </cell>
+          <cell r="O27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="F28">
+            <v>0</v>
+          </cell>
+          <cell r="M28">
+            <v>0</v>
+          </cell>
+          <cell r="N28">
+            <v>0</v>
+          </cell>
+          <cell r="O28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="F29">
+            <v>0</v>
+          </cell>
+          <cell r="M29">
+            <v>0</v>
+          </cell>
+          <cell r="N29">
+            <v>0</v>
+          </cell>
+          <cell r="O29">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="F30">
+            <v>0</v>
+          </cell>
+          <cell r="M30">
+            <v>0</v>
+          </cell>
+          <cell r="N30">
+            <v>0</v>
+          </cell>
+          <cell r="O30">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="F31">
+            <v>0</v>
+          </cell>
+          <cell r="M31">
+            <v>0</v>
+          </cell>
+          <cell r="N31">
+            <v>0</v>
+          </cell>
+          <cell r="O31">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="F32">
+            <v>0</v>
+          </cell>
+          <cell r="M32">
+            <v>0</v>
+          </cell>
+          <cell r="N32">
+            <v>0</v>
+          </cell>
+          <cell r="O32">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="F33">
+            <v>0</v>
+          </cell>
+          <cell r="M33">
+            <v>0</v>
+          </cell>
+          <cell r="N33">
+            <v>0</v>
+          </cell>
+          <cell r="O33">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="F34">
+            <v>0</v>
+          </cell>
+          <cell r="M34">
+            <v>0</v>
+          </cell>
+          <cell r="N34">
+            <v>0</v>
+          </cell>
+          <cell r="O34">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="F35">
+            <v>0</v>
+          </cell>
+          <cell r="M35">
+            <v>0</v>
+          </cell>
+          <cell r="N35">
+            <v>0</v>
+          </cell>
+          <cell r="O35">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="F36">
+            <v>0</v>
+          </cell>
+          <cell r="M36">
+            <v>0</v>
+          </cell>
+          <cell r="N36">
+            <v>0</v>
+          </cell>
+          <cell r="O36">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="F37">
+            <v>0</v>
+          </cell>
+          <cell r="M37">
+            <v>0</v>
+          </cell>
+          <cell r="N37">
+            <v>0</v>
+          </cell>
+          <cell r="O37">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="F38">
+            <v>0</v>
+          </cell>
+          <cell r="M38">
+            <v>0</v>
+          </cell>
+          <cell r="N38">
+            <v>0</v>
+          </cell>
+          <cell r="O38">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="F39">
+            <v>0</v>
+          </cell>
+          <cell r="M39">
+            <v>0</v>
+          </cell>
+          <cell r="N39">
+            <v>0</v>
+          </cell>
+          <cell r="O39">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="F40">
+            <v>0</v>
+          </cell>
+          <cell r="M40">
+            <v>0</v>
+          </cell>
+          <cell r="N40">
+            <v>0</v>
+          </cell>
+          <cell r="O40">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="F41">
+            <v>0</v>
+          </cell>
+          <cell r="M41">
+            <v>0</v>
+          </cell>
+          <cell r="N41">
+            <v>0</v>
+          </cell>
+          <cell r="O41">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="F42">
+            <v>0</v>
+          </cell>
+          <cell r="M42">
+            <v>0</v>
+          </cell>
+          <cell r="N42">
+            <v>0</v>
+          </cell>
+          <cell r="O42">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="F43">
+            <v>0</v>
+          </cell>
+          <cell r="M43">
+            <v>0</v>
+          </cell>
+          <cell r="N43">
+            <v>0</v>
+          </cell>
+          <cell r="O43">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="F44">
+            <v>0</v>
+          </cell>
+          <cell r="M44">
+            <v>0</v>
+          </cell>
+          <cell r="N44">
+            <v>0</v>
+          </cell>
+          <cell r="O44">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="F45">
+            <v>0</v>
+          </cell>
+          <cell r="M45">
+            <v>0</v>
+          </cell>
+          <cell r="N45">
+            <v>0</v>
+          </cell>
+          <cell r="O45">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="F46">
+            <v>0</v>
+          </cell>
+          <cell r="M46">
+            <v>0</v>
+          </cell>
+          <cell r="N46">
+            <v>0</v>
+          </cell>
+          <cell r="O46">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="F47">
+            <v>0</v>
+          </cell>
+          <cell r="M47">
+            <v>0</v>
+          </cell>
+          <cell r="N47">
+            <v>0</v>
+          </cell>
+          <cell r="O47">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="F48">
+            <v>0</v>
+          </cell>
+          <cell r="M48">
+            <v>0</v>
+          </cell>
+          <cell r="N48">
+            <v>0</v>
+          </cell>
+          <cell r="O48">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="F49">
+            <v>0</v>
+          </cell>
+          <cell r="M49">
+            <v>0</v>
+          </cell>
+          <cell r="N49">
+            <v>0</v>
+          </cell>
+          <cell r="O49">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="F50">
+            <v>0</v>
+          </cell>
+          <cell r="M50">
+            <v>0</v>
+          </cell>
+          <cell r="N50">
+            <v>0</v>
+          </cell>
+          <cell r="O50">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="F51">
+            <v>0</v>
+          </cell>
+          <cell r="M51">
+            <v>0</v>
+          </cell>
+          <cell r="N51">
+            <v>0</v>
+          </cell>
+          <cell r="O51">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="F52">
+            <v>0</v>
+          </cell>
+          <cell r="M52">
+            <v>0</v>
+          </cell>
+          <cell r="N52">
+            <v>0</v>
+          </cell>
+          <cell r="O52">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="F53">
+            <v>0</v>
+          </cell>
+          <cell r="M53">
+            <v>0</v>
+          </cell>
+          <cell r="N53">
+            <v>0</v>
+          </cell>
+          <cell r="O53">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="F54">
+            <v>0</v>
+          </cell>
+          <cell r="M54">
+            <v>0</v>
+          </cell>
+          <cell r="N54">
+            <v>0</v>
+          </cell>
+          <cell r="O54">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="F55">
+            <v>0</v>
+          </cell>
+          <cell r="M55">
+            <v>0</v>
+          </cell>
+          <cell r="N55">
+            <v>0</v>
+          </cell>
+          <cell r="O55">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="F57">
+            <v>0</v>
+          </cell>
+          <cell r="M57">
+            <v>0</v>
+          </cell>
+          <cell r="N57">
+            <v>0</v>
+          </cell>
+          <cell r="O57">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="F58">
+            <v>0</v>
+          </cell>
+          <cell r="M58">
+            <v>0</v>
+          </cell>
+          <cell r="N58">
+            <v>0</v>
+          </cell>
+          <cell r="O58">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="F59">
+            <v>0</v>
+          </cell>
+          <cell r="M59">
+            <v>0</v>
+          </cell>
+          <cell r="N59">
+            <v>0</v>
+          </cell>
+          <cell r="O59">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="F60">
+            <v>0</v>
+          </cell>
+          <cell r="M60">
+            <v>0</v>
+          </cell>
+          <cell r="N60">
+            <v>0</v>
+          </cell>
+          <cell r="O60">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="F61">
+            <v>0</v>
+          </cell>
+          <cell r="M61">
+            <v>0</v>
+          </cell>
+          <cell r="N61">
+            <v>0</v>
+          </cell>
+          <cell r="O61">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="F62">
+            <v>0</v>
+          </cell>
+          <cell r="M62">
+            <v>0</v>
+          </cell>
+          <cell r="N62">
+            <v>0</v>
+          </cell>
+          <cell r="O62">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="F63">
+            <v>0</v>
+          </cell>
+          <cell r="M63">
+            <v>0</v>
+          </cell>
+          <cell r="N63">
+            <v>0</v>
+          </cell>
+          <cell r="O63">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="F64">
+            <v>0</v>
+          </cell>
+          <cell r="M64">
+            <v>0</v>
+          </cell>
+          <cell r="N64">
+            <v>0</v>
+          </cell>
+          <cell r="O64">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="F65">
+            <v>0</v>
+          </cell>
+          <cell r="M65">
+            <v>0</v>
+          </cell>
+          <cell r="N65">
+            <v>0</v>
+          </cell>
+          <cell r="O65">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="F66">
+            <v>0</v>
+          </cell>
+          <cell r="M66">
+            <v>0</v>
+          </cell>
+          <cell r="N66">
+            <v>0</v>
+          </cell>
+          <cell r="O66">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="F67">
+            <v>0</v>
+          </cell>
+          <cell r="M67">
+            <v>0</v>
+          </cell>
+          <cell r="N67">
+            <v>0</v>
+          </cell>
+          <cell r="O67">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="F68">
+            <v>0</v>
+          </cell>
+          <cell r="M68">
+            <v>0</v>
+          </cell>
+          <cell r="N68">
+            <v>0</v>
+          </cell>
+          <cell r="O68">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="F69">
+            <v>0</v>
+          </cell>
+          <cell r="M69">
+            <v>0</v>
+          </cell>
+          <cell r="N69">
+            <v>0</v>
+          </cell>
+          <cell r="O69">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="F70">
+            <v>0</v>
+          </cell>
+          <cell r="M70">
+            <v>0</v>
+          </cell>
+          <cell r="N70">
+            <v>0</v>
+          </cell>
+          <cell r="O70">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="F71">
+            <v>0</v>
+          </cell>
+          <cell r="M71">
+            <v>0</v>
+          </cell>
+          <cell r="N71">
+            <v>0</v>
+          </cell>
+          <cell r="O71">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="F72">
+            <v>0</v>
+          </cell>
+          <cell r="M72">
+            <v>0</v>
+          </cell>
+          <cell r="N72">
+            <v>0</v>
+          </cell>
+          <cell r="O72">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="F73">
+            <v>0</v>
+          </cell>
+          <cell r="M73">
+            <v>0</v>
+          </cell>
+          <cell r="N73">
+            <v>0</v>
+          </cell>
+          <cell r="O73">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="F74">
+            <v>0</v>
+          </cell>
+          <cell r="M74">
+            <v>0</v>
+          </cell>
+          <cell r="N74">
+            <v>0</v>
+          </cell>
+          <cell r="O74">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="F75">
+            <v>0</v>
+          </cell>
+          <cell r="M75">
+            <v>0</v>
+          </cell>
+          <cell r="N75">
+            <v>0</v>
+          </cell>
+          <cell r="O75">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="F76">
+            <v>0</v>
+          </cell>
+          <cell r="M76">
+            <v>0</v>
+          </cell>
+          <cell r="N76">
+            <v>0</v>
+          </cell>
+          <cell r="O76">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="F77">
+            <v>0</v>
+          </cell>
+          <cell r="M77">
+            <v>0</v>
+          </cell>
+          <cell r="N77">
+            <v>0</v>
+          </cell>
+          <cell r="O77">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="F78">
+            <v>0</v>
+          </cell>
+          <cell r="M78">
+            <v>0</v>
+          </cell>
+          <cell r="N78">
+            <v>0</v>
+          </cell>
+          <cell r="O78">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="F79">
+            <v>0</v>
+          </cell>
+          <cell r="M79">
+            <v>0</v>
+          </cell>
+          <cell r="N79">
+            <v>0</v>
+          </cell>
+          <cell r="O79">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="F80">
+            <v>0</v>
+          </cell>
+          <cell r="M80">
+            <v>0</v>
+          </cell>
+          <cell r="N80">
+            <v>0</v>
+          </cell>
+          <cell r="O80">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="F81">
+            <v>0</v>
+          </cell>
+          <cell r="M81">
+            <v>0</v>
+          </cell>
+          <cell r="N81">
+            <v>0</v>
+          </cell>
+          <cell r="O81">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="F82">
+            <v>0</v>
+          </cell>
+          <cell r="M82">
+            <v>0</v>
+          </cell>
+          <cell r="N82">
+            <v>0</v>
+          </cell>
+          <cell r="O82">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="F83">
+            <v>0</v>
+          </cell>
+          <cell r="M83">
+            <v>0</v>
+          </cell>
+          <cell r="N83">
+            <v>0</v>
+          </cell>
+          <cell r="O83">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="F84">
+            <v>0</v>
+          </cell>
+          <cell r="M84">
+            <v>0</v>
+          </cell>
+          <cell r="N84">
+            <v>0</v>
+          </cell>
+          <cell r="O84">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="F85">
+            <v>0</v>
+          </cell>
+          <cell r="M85">
+            <v>0</v>
+          </cell>
+          <cell r="N85">
+            <v>0</v>
+          </cell>
+          <cell r="O85">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="F86">
+            <v>0</v>
+          </cell>
+          <cell r="M86">
+            <v>0</v>
+          </cell>
+          <cell r="N86">
+            <v>0</v>
+          </cell>
+          <cell r="O86">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="F87">
+            <v>0</v>
+          </cell>
+          <cell r="M87">
+            <v>0</v>
+          </cell>
+          <cell r="N87">
+            <v>0</v>
+          </cell>
+          <cell r="O87">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="F88">
+            <v>0</v>
+          </cell>
+          <cell r="M88">
+            <v>0</v>
+          </cell>
+          <cell r="N88">
+            <v>0</v>
+          </cell>
+          <cell r="O88">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="F89">
+            <v>0</v>
+          </cell>
+          <cell r="M89">
+            <v>0</v>
+          </cell>
+          <cell r="N89">
+            <v>0</v>
+          </cell>
+          <cell r="O89">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="F90">
+            <v>0</v>
+          </cell>
+          <cell r="M90">
+            <v>0</v>
+          </cell>
+          <cell r="N90">
+            <v>0</v>
+          </cell>
+          <cell r="O90">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="F91">
+            <v>0</v>
+          </cell>
+          <cell r="M91">
+            <v>0</v>
+          </cell>
+          <cell r="N91">
+            <v>0</v>
+          </cell>
+          <cell r="O91">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="F92">
+            <v>0</v>
+          </cell>
+          <cell r="M92">
+            <v>0</v>
+          </cell>
+          <cell r="N92">
+            <v>0</v>
+          </cell>
+          <cell r="O92">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="F93">
+            <v>0</v>
+          </cell>
+          <cell r="M93">
+            <v>0</v>
+          </cell>
+          <cell r="N93">
+            <v>0</v>
+          </cell>
+          <cell r="O93">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="F94">
+            <v>0</v>
+          </cell>
+          <cell r="M94">
+            <v>0</v>
+          </cell>
+          <cell r="N94">
+            <v>0</v>
+          </cell>
+          <cell r="O94">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="F95">
+            <v>0</v>
+          </cell>
+          <cell r="M95">
+            <v>0</v>
+          </cell>
+          <cell r="N95">
+            <v>0</v>
+          </cell>
+          <cell r="O95">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="F96">
+            <v>0</v>
+          </cell>
+          <cell r="M96">
+            <v>0</v>
+          </cell>
+          <cell r="N96">
+            <v>0</v>
+          </cell>
+          <cell r="O96">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="F97">
+            <v>0</v>
+          </cell>
+          <cell r="M97">
+            <v>0</v>
+          </cell>
+          <cell r="N97">
+            <v>0</v>
+          </cell>
+          <cell r="O97">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="F98">
+            <v>0</v>
+          </cell>
+          <cell r="M98">
+            <v>0</v>
+          </cell>
+          <cell r="N98">
+            <v>0</v>
+          </cell>
+          <cell r="O98">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="F99">
+            <v>0</v>
+          </cell>
+          <cell r="M99">
+            <v>0</v>
+          </cell>
+          <cell r="N99">
+            <v>0</v>
+          </cell>
+          <cell r="O99">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="F100">
+            <v>0</v>
+          </cell>
+          <cell r="M100">
+            <v>0</v>
+          </cell>
+          <cell r="N100">
+            <v>0</v>
+          </cell>
+          <cell r="O100">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="F102">
+            <v>0</v>
+          </cell>
+          <cell r="M102">
+            <v>0</v>
+          </cell>
+          <cell r="N102">
+            <v>0</v>
+          </cell>
+          <cell r="O102">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="F103">
+            <v>0</v>
+          </cell>
+          <cell r="M103">
+            <v>0</v>
+          </cell>
+          <cell r="N103">
+            <v>0</v>
+          </cell>
+          <cell r="O103">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="F104">
+            <v>0</v>
+          </cell>
+          <cell r="M104">
+            <v>0</v>
+          </cell>
+          <cell r="N104">
+            <v>0</v>
+          </cell>
+          <cell r="O104">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="F105">
+            <v>0</v>
+          </cell>
+          <cell r="M105">
+            <v>0</v>
+          </cell>
+          <cell r="N105">
+            <v>0</v>
+          </cell>
+          <cell r="O105">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="F106">
+            <v>0</v>
+          </cell>
+          <cell r="M106">
+            <v>0</v>
+          </cell>
+          <cell r="N106">
+            <v>0</v>
+          </cell>
+          <cell r="O106">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="F107">
+            <v>0</v>
+          </cell>
+          <cell r="M107">
+            <v>0</v>
+          </cell>
+          <cell r="N107">
+            <v>0</v>
+          </cell>
+          <cell r="O107">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="F108">
+            <v>0</v>
+          </cell>
+          <cell r="M108">
+            <v>0</v>
+          </cell>
+          <cell r="N108">
+            <v>0</v>
+          </cell>
+          <cell r="O108">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="F109">
+            <v>0</v>
+          </cell>
+          <cell r="M109">
+            <v>0</v>
+          </cell>
+          <cell r="N109">
+            <v>0</v>
+          </cell>
+          <cell r="O109">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="F110">
+            <v>0</v>
+          </cell>
+          <cell r="M110">
+            <v>0</v>
+          </cell>
+          <cell r="N110">
+            <v>0</v>
+          </cell>
+          <cell r="O110">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="F111">
+            <v>0</v>
+          </cell>
+          <cell r="M111">
+            <v>0</v>
+          </cell>
+          <cell r="N111">
+            <v>0</v>
+          </cell>
+          <cell r="O111">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="F112">
+            <v>0</v>
+          </cell>
+          <cell r="M112">
+            <v>0</v>
+          </cell>
+          <cell r="N112">
+            <v>0</v>
+          </cell>
+          <cell r="O112">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="F113">
+            <v>0</v>
+          </cell>
+          <cell r="M113">
+            <v>0</v>
+          </cell>
+          <cell r="N113">
+            <v>0</v>
+          </cell>
+          <cell r="O113">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="F114">
+            <v>0</v>
+          </cell>
+          <cell r="M114">
+            <v>0</v>
+          </cell>
+          <cell r="N114">
+            <v>0</v>
+          </cell>
+          <cell r="O114">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="F115">
+            <v>0</v>
+          </cell>
+          <cell r="M115">
+            <v>0</v>
+          </cell>
+          <cell r="N115">
+            <v>0</v>
+          </cell>
+          <cell r="O115">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="F116">
+            <v>0</v>
+          </cell>
+          <cell r="M116">
+            <v>0</v>
+          </cell>
+          <cell r="N116">
+            <v>0</v>
+          </cell>
+          <cell r="O116">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="F117">
+            <v>0</v>
+          </cell>
+          <cell r="M117">
+            <v>0</v>
+          </cell>
+          <cell r="N117">
+            <v>0</v>
+          </cell>
+          <cell r="O117">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="4">
+          <cell r="L4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="L7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="L8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="L9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="L10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="L12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="L13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="L14">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="L15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="L17">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="L19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="L20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="L21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="L22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="L23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="L24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="L25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="L26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="L27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="L28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="L29">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="L30">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="L31">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="L32">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="L33">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="L34">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="L35">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="L36">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="L37">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="L38">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="L39">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="L40">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="L41">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="L42">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="L43">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="L44">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="L45">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="L46">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="L47">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="L48">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="L49">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="L50">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="L51">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="L52">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="L53">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="L54">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="L55">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="L57">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="L58">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="L59">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="L60">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="L61">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="L62">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="L63">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="L64">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="L65">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="L66">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="L67">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="L68">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="L69">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="L70">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="L71">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="L72">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="L73">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="L74">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="L75">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="L76">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="L77">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="L78">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="L79">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="L80">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="L81">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="L82">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="L83">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="L84">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="L85">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="L86">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="L87">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="L88">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="L89">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="L90">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="L91">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="L92">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="L93">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="L94">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="L95">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="L96">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="L97">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="L98">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="L99">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="L100">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="L102">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="L103">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="L104">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="L105">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="L106">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="L107">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="L108">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="L109">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="L110">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="L111">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="L112">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="L113">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="L114">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="L115">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="L116">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="L117">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1463,18 +3634,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="1.109375" customWidth="1"/>
+    <col min="4" max="16" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -1482,21 +3656,55 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:16" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="65" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="65" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="65" t="s">
+        <v>149</v>
+      </c>
+      <c r="I3" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="J3" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="K3" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="N3" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="O3" s="65" t="s">
+        <v>78</v>
+      </c>
+      <c r="P3" s="65" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1506,8 +3714,36 @@
       <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="str">
+        <f>HYPERLINK([1]اضافات!N4)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <f>HYPERLINK([1]اضافات!M4)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" t="str">
+        <f>HYPERLINK([1]اضافات!F4)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" t="str">
+        <f>HYPERLINK([1]اضافات!O4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" t="str">
+        <f>HYPERLINK([1]خصومات!L4)</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>SUM(D4,VALUE(E4),VALUE(F4),VALUE(G4))</f>
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f>VALUE(D4)+VALUE(G4)+VALUE(H4)-VALUE(I4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1517,8 +3753,36 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="str">
+        <f>HYPERLINK([1]اضافات!N5)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" t="str">
+        <f>HYPERLINK([1]اضافات!M5)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <f>HYPERLINK([1]اضافات!F5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
+        <f>HYPERLINK([1]اضافات!O5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" t="str">
+        <f>HYPERLINK([1]خصومات!L5)</f>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f t="shared" ref="J5:J68" si="0">SUM(D5,VALUE(E5),VALUE(F5),VALUE(G5))</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f t="shared" ref="K5:K68" si="1">VALUE(D5)+VALUE(G5)+VALUE(H5)-VALUE(I5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1528,96 +3792,432 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="str">
+        <f>HYPERLINK([1]اضافات!N6)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" t="str">
+        <f>HYPERLINK([1]اضافات!M6)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <f>HYPERLINK([1]اضافات!F6)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" t="str">
+        <f>HYPERLINK([1]اضافات!O6)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" t="str">
+        <f>HYPERLINK([1]خصومات!L6)</f>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="str">
+        <f>HYPERLINK([1]اضافات!N7)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" t="str">
+        <f>HYPERLINK([1]اضافات!M7)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <f>HYPERLINK([1]اضافات!F7)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <f>HYPERLINK([1]اضافات!O7)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" t="str">
+        <f>HYPERLINK([1]خصومات!L7)</f>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="str">
+        <f>HYPERLINK([1]اضافات!N8)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" t="str">
+        <f>HYPERLINK([1]اضافات!M8)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
+        <f>HYPERLINK([1]اضافات!F8)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" t="str">
+        <f>HYPERLINK([1]اضافات!O8)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <f>HYPERLINK([1]خصومات!L8)</f>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" t="str">
+        <f>HYPERLINK([1]اضافات!N9)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" t="str">
+        <f>HYPERLINK([1]اضافات!M9)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <f>HYPERLINK([1]اضافات!F9)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" t="str">
+        <f>HYPERLINK([1]اضافات!O9)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
+        <f>HYPERLINK([1]خصومات!L9)</f>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="str">
+        <f>HYPERLINK([1]اضافات!N10)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" t="str">
+        <f>HYPERLINK([1]اضافات!M10)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" t="str">
+        <f>HYPERLINK([1]اضافات!F10)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" t="str">
+        <f>HYPERLINK([1]اضافات!O10)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
+        <f>HYPERLINK([1]خصومات!L10)</f>
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" t="str">
+        <f>HYPERLINK([1]اضافات!N11)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" t="str">
+        <f>HYPERLINK([1]اضافات!M11)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" t="str">
+        <f>HYPERLINK([1]اضافات!F11)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" t="str">
+        <f>HYPERLINK([1]اضافات!O11)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <f>HYPERLINK([1]خصومات!L11)</f>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" t="str">
+        <f>HYPERLINK([1]اضافات!N12)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" t="str">
+        <f>HYPERLINK([1]اضافات!M12)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <f>HYPERLINK([1]اضافات!F12)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" t="str">
+        <f>HYPERLINK([1]اضافات!O12)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" t="str">
+        <f>HYPERLINK([1]خصومات!L12)</f>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" t="str">
+        <f>HYPERLINK([1]اضافات!N13)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" t="str">
+        <f>HYPERLINK([1]اضافات!M13)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <f>HYPERLINK([1]اضافات!F13)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" t="str">
+        <f>HYPERLINK([1]اضافات!O13)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" t="str">
+        <f>HYPERLINK([1]خصومات!L13)</f>
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" t="str">
+        <f>HYPERLINK([1]اضافات!N14)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <f>HYPERLINK([1]اضافات!M14)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <f>HYPERLINK([1]اضافات!F14)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" t="str">
+        <f>HYPERLINK([1]اضافات!O14)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" t="str">
+        <f>HYPERLINK([1]خصومات!L14)</f>
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" t="str">
+        <f>HYPERLINK([1]اضافات!N15)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" t="str">
+        <f>HYPERLINK([1]اضافات!M15)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <f>HYPERLINK([1]اضافات!F15)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" t="str">
+        <f>HYPERLINK([1]اضافات!O15)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" t="str">
+        <f>HYPERLINK([1]خصومات!L15)</f>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" t="str">
+        <f>HYPERLINK([1]اضافات!N16)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" t="str">
+        <f>HYPERLINK([1]اضافات!M16)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" t="str">
+        <f>HYPERLINK([1]اضافات!F16)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" t="str">
+        <f>HYPERLINK([1]اضافات!O16)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" t="str">
+        <f>HYPERLINK([1]خصومات!L16)</f>
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="str">
+        <f>HYPERLINK([1]اضافات!N17)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" t="str">
+        <f>HYPERLINK([1]اضافات!M17)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" t="str">
+        <f>HYPERLINK([1]اضافات!F17)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" t="str">
+        <f>HYPERLINK([1]اضافات!O17)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" t="str">
+        <f>HYPERLINK([1]خصومات!L17)</f>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>3</v>
       </c>
@@ -1628,8 +4228,40 @@
         <f>SUM(D4:D17)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18">
+        <f t="shared" ref="E18:K18" si="2">SUM(E4:E17)</f>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <f>SUM(K4:K17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -1639,8 +4271,36 @@
       <c r="D19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="str">
+        <f>HYPERLINK([1]اضافات!N19)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" t="str">
+        <f>HYPERLINK([1]اضافات!M19)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" t="str">
+        <f>HYPERLINK([1]اضافات!F19)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" t="str">
+        <f>HYPERLINK([1]اضافات!O19)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" t="str">
+        <f>HYPERLINK([1]خصومات!L19)</f>
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1650,8 +4310,36 @@
       <c r="D20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" t="str">
+        <f>HYPERLINK([1]اضافات!N20)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" t="str">
+        <f>HYPERLINK([1]اضافات!M20)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" t="str">
+        <f>HYPERLINK([1]اضافات!F20)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" t="str">
+        <f>HYPERLINK([1]اضافات!O20)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" t="str">
+        <f>HYPERLINK([1]خصومات!L20)</f>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1661,8 +4349,36 @@
       <c r="D21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" t="str">
+        <f>HYPERLINK([1]اضافات!N21)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" t="str">
+        <f>HYPERLINK([1]اضافات!M21)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" t="str">
+        <f>HYPERLINK([1]اضافات!F21)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" t="str">
+        <f>HYPERLINK([1]اضافات!O21)</f>
+        <v>0</v>
+      </c>
+      <c r="I21" t="str">
+        <f>HYPERLINK([1]خصومات!L21)</f>
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>4</v>
       </c>
@@ -1672,8 +4388,36 @@
       <c r="D22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" t="str">
+        <f>HYPERLINK([1]اضافات!N22)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" t="str">
+        <f>HYPERLINK([1]اضافات!M22)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" t="str">
+        <f>HYPERLINK([1]اضافات!F22)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" t="str">
+        <f>HYPERLINK([1]اضافات!O22)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" t="str">
+        <f>HYPERLINK([1]خصومات!L22)</f>
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>5</v>
       </c>
@@ -1683,8 +4427,36 @@
       <c r="D23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" t="str">
+        <f>HYPERLINK([1]اضافات!N23)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" t="str">
+        <f>HYPERLINK([1]اضافات!M23)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" t="str">
+        <f>HYPERLINK([1]اضافات!F23)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" t="str">
+        <f>HYPERLINK([1]اضافات!O23)</f>
+        <v>0</v>
+      </c>
+      <c r="I23" t="str">
+        <f>HYPERLINK([1]خصومات!L23)</f>
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>6</v>
       </c>
@@ -1694,8 +4466,36 @@
       <c r="D24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" t="str">
+        <f>HYPERLINK([1]اضافات!N24)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" t="str">
+        <f>HYPERLINK([1]اضافات!M24)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" t="str">
+        <f>HYPERLINK([1]اضافات!F24)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" t="str">
+        <f>HYPERLINK([1]اضافات!O24)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" t="str">
+        <f>HYPERLINK([1]خصومات!L24)</f>
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>7</v>
       </c>
@@ -1705,64 +4505,288 @@
       <c r="D25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" t="str">
+        <f>HYPERLINK([1]اضافات!N25)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" t="str">
+        <f>HYPERLINK([1]اضافات!M25)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" t="str">
+        <f>HYPERLINK([1]اضافات!F25)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" t="str">
+        <f>HYPERLINK([1]اضافات!O25)</f>
+        <v>0</v>
+      </c>
+      <c r="I25" t="str">
+        <f>HYPERLINK([1]خصومات!L25)</f>
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" t="str">
+        <f>HYPERLINK([1]اضافات!N26)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" t="str">
+        <f>HYPERLINK([1]اضافات!M26)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" t="str">
+        <f>HYPERLINK([1]اضافات!F26)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" t="str">
+        <f>HYPERLINK([1]اضافات!O26)</f>
+        <v>0</v>
+      </c>
+      <c r="I26" t="str">
+        <f>HYPERLINK([1]خصومات!L26)</f>
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" t="str">
+        <f>HYPERLINK([1]اضافات!N27)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" t="str">
+        <f>HYPERLINK([1]اضافات!M27)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" t="str">
+        <f>HYPERLINK([1]اضافات!F27)</f>
+        <v>0</v>
+      </c>
+      <c r="H27" t="str">
+        <f>HYPERLINK([1]اضافات!O27)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" t="str">
+        <f>HYPERLINK([1]خصومات!L27)</f>
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" t="str">
+        <f>HYPERLINK([1]اضافات!N28)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" t="str">
+        <f>HYPERLINK([1]اضافات!M28)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" t="str">
+        <f>HYPERLINK([1]اضافات!F28)</f>
+        <v>0</v>
+      </c>
+      <c r="H28" t="str">
+        <f>HYPERLINK([1]اضافات!O28)</f>
+        <v>0</v>
+      </c>
+      <c r="I28" t="str">
+        <f>HYPERLINK([1]خصومات!L28)</f>
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" t="str">
+        <f>HYPERLINK([1]اضافات!N29)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" t="str">
+        <f>HYPERLINK([1]اضافات!M29)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" t="str">
+        <f>HYPERLINK([1]اضافات!F29)</f>
+        <v>0</v>
+      </c>
+      <c r="H29" t="str">
+        <f>HYPERLINK([1]اضافات!O29)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" t="str">
+        <f>HYPERLINK([1]خصومات!L29)</f>
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" t="str">
+        <f>HYPERLINK([1]اضافات!N30)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" t="str">
+        <f>HYPERLINK([1]اضافات!M30)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" t="str">
+        <f>HYPERLINK([1]اضافات!F30)</f>
+        <v>0</v>
+      </c>
+      <c r="H30" t="str">
+        <f>HYPERLINK([1]اضافات!O30)</f>
+        <v>0</v>
+      </c>
+      <c r="I30" t="str">
+        <f>HYPERLINK([1]خصومات!L30)</f>
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" t="str">
+        <f>HYPERLINK([1]اضافات!N31)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" t="str">
+        <f>HYPERLINK([1]اضافات!M31)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" t="str">
+        <f>HYPERLINK([1]اضافات!F31)</f>
+        <v>0</v>
+      </c>
+      <c r="H31" t="str">
+        <f>HYPERLINK([1]اضافات!O31)</f>
+        <v>0</v>
+      </c>
+      <c r="I31" t="str">
+        <f>HYPERLINK([1]خصومات!L31)</f>
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" t="str">
+        <f>HYPERLINK([1]اضافات!N32)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" t="str">
+        <f>HYPERLINK([1]اضافات!M32)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" t="str">
+        <f>HYPERLINK([1]اضافات!F32)</f>
+        <v>0</v>
+      </c>
+      <c r="H32" t="str">
+        <f>HYPERLINK([1]اضافات!O32)</f>
+        <v>0</v>
+      </c>
+      <c r="I32" t="str">
+        <f>HYPERLINK([1]خصومات!L32)</f>
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>8</v>
       </c>
@@ -1772,8 +4796,36 @@
       <c r="D33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" t="str">
+        <f>HYPERLINK([1]اضافات!N33)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" t="str">
+        <f>HYPERLINK([1]اضافات!M33)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" t="str">
+        <f>HYPERLINK([1]اضافات!F33)</f>
+        <v>0</v>
+      </c>
+      <c r="H33" t="str">
+        <f>HYPERLINK([1]اضافات!O33)</f>
+        <v>0</v>
+      </c>
+      <c r="I33" t="str">
+        <f>HYPERLINK([1]خصومات!L33)</f>
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>9</v>
       </c>
@@ -1783,8 +4835,36 @@
       <c r="D34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" t="str">
+        <f>HYPERLINK([1]اضافات!N34)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" t="str">
+        <f>HYPERLINK([1]اضافات!M34)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" t="str">
+        <f>HYPERLINK([1]اضافات!F34)</f>
+        <v>0</v>
+      </c>
+      <c r="H34" t="str">
+        <f>HYPERLINK([1]اضافات!O34)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" t="str">
+        <f>HYPERLINK([1]خصومات!L34)</f>
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>10</v>
       </c>
@@ -1794,80 +4874,360 @@
       <c r="D35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" t="str">
+        <f>HYPERLINK([1]اضافات!N35)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" t="str">
+        <f>HYPERLINK([1]اضافات!M35)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" t="str">
+        <f>HYPERLINK([1]اضافات!F35)</f>
+        <v>0</v>
+      </c>
+      <c r="H35" t="str">
+        <f>HYPERLINK([1]اضافات!O35)</f>
+        <v>0</v>
+      </c>
+      <c r="I35" t="str">
+        <f>HYPERLINK([1]خصومات!L35)</f>
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" t="str">
+        <f>HYPERLINK([1]اضافات!N36)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" t="str">
+        <f>HYPERLINK([1]اضافات!M36)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" t="str">
+        <f>HYPERLINK([1]اضافات!F36)</f>
+        <v>0</v>
+      </c>
+      <c r="H36" t="str">
+        <f>HYPERLINK([1]اضافات!O36)</f>
+        <v>0</v>
+      </c>
+      <c r="I36" t="str">
+        <f>HYPERLINK([1]خصومات!L36)</f>
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>9</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" t="str">
+        <f>HYPERLINK([1]اضافات!N37)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" t="str">
+        <f>HYPERLINK([1]اضافات!M37)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" t="str">
+        <f>HYPERLINK([1]اضافات!F37)</f>
+        <v>0</v>
+      </c>
+      <c r="H37" t="str">
+        <f>HYPERLINK([1]اضافات!O37)</f>
+        <v>0</v>
+      </c>
+      <c r="I37" t="str">
+        <f>HYPERLINK([1]خصومات!L37)</f>
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>9</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" t="str">
+        <f>HYPERLINK([1]اضافات!N38)</f>
+        <v>0</v>
+      </c>
+      <c r="F38" t="str">
+        <f>HYPERLINK([1]اضافات!M38)</f>
+        <v>0</v>
+      </c>
+      <c r="G38" t="str">
+        <f>HYPERLINK([1]اضافات!F38)</f>
+        <v>0</v>
+      </c>
+      <c r="H38" t="str">
+        <f>HYPERLINK([1]اضافات!O38)</f>
+        <v>0</v>
+      </c>
+      <c r="I38" t="str">
+        <f>HYPERLINK([1]خصومات!L38)</f>
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" t="str">
+        <f>HYPERLINK([1]اضافات!N39)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" t="str">
+        <f>HYPERLINK([1]اضافات!M39)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" t="str">
+        <f>HYPERLINK([1]اضافات!F39)</f>
+        <v>0</v>
+      </c>
+      <c r="H39" t="str">
+        <f>HYPERLINK([1]اضافات!O39)</f>
+        <v>0</v>
+      </c>
+      <c r="I39" t="str">
+        <f>HYPERLINK([1]خصومات!L39)</f>
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>9</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" t="str">
+        <f>HYPERLINK([1]اضافات!N40)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" t="str">
+        <f>HYPERLINK([1]اضافات!M40)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" t="str">
+        <f>HYPERLINK([1]اضافات!F40)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" t="str">
+        <f>HYPERLINK([1]اضافات!O40)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" t="str">
+        <f>HYPERLINK([1]خصومات!L40)</f>
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>9</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" t="str">
+        <f>HYPERLINK([1]اضافات!N41)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" t="str">
+        <f>HYPERLINK([1]اضافات!M41)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" t="str">
+        <f>HYPERLINK([1]اضافات!F41)</f>
+        <v>0</v>
+      </c>
+      <c r="H41" t="str">
+        <f>HYPERLINK([1]اضافات!O41)</f>
+        <v>0</v>
+      </c>
+      <c r="I41" t="str">
+        <f>HYPERLINK([1]خصومات!L41)</f>
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>9</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" t="str">
+        <f>HYPERLINK([1]اضافات!N42)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" t="str">
+        <f>HYPERLINK([1]اضافات!M42)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" t="str">
+        <f>HYPERLINK([1]اضافات!F42)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" t="str">
+        <f>HYPERLINK([1]اضافات!O42)</f>
+        <v>0</v>
+      </c>
+      <c r="I42" t="str">
+        <f>HYPERLINK([1]خصومات!L42)</f>
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>9</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" t="str">
+        <f>HYPERLINK([1]اضافات!N43)</f>
+        <v>0</v>
+      </c>
+      <c r="F43" t="str">
+        <f>HYPERLINK([1]اضافات!M43)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" t="str">
+        <f>HYPERLINK([1]اضافات!F43)</f>
+        <v>0</v>
+      </c>
+      <c r="H43" t="str">
+        <f>HYPERLINK([1]اضافات!O43)</f>
+        <v>0</v>
+      </c>
+      <c r="I43" t="str">
+        <f>HYPERLINK([1]خصومات!L43)</f>
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>9</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" t="str">
+        <f>HYPERLINK([1]اضافات!N44)</f>
+        <v>0</v>
+      </c>
+      <c r="F44" t="str">
+        <f>HYPERLINK([1]اضافات!M44)</f>
+        <v>0</v>
+      </c>
+      <c r="G44" t="str">
+        <f>HYPERLINK([1]اضافات!F44)</f>
+        <v>0</v>
+      </c>
+      <c r="H44" t="str">
+        <f>HYPERLINK([1]اضافات!O44)</f>
+        <v>0</v>
+      </c>
+      <c r="I44" t="str">
+        <f>HYPERLINK([1]خصومات!L44)</f>
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>11</v>
       </c>
@@ -1877,8 +5237,36 @@
       <c r="D45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" t="str">
+        <f>HYPERLINK([1]اضافات!N45)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" t="str">
+        <f>HYPERLINK([1]اضافات!M45)</f>
+        <v>0</v>
+      </c>
+      <c r="G45" t="str">
+        <f>HYPERLINK([1]اضافات!F45)</f>
+        <v>0</v>
+      </c>
+      <c r="H45" t="str">
+        <f>HYPERLINK([1]اضافات!O45)</f>
+        <v>0</v>
+      </c>
+      <c r="I45" t="str">
+        <f>HYPERLINK([1]خصومات!L45)</f>
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>12</v>
       </c>
@@ -1888,8 +5276,36 @@
       <c r="D46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" t="str">
+        <f>HYPERLINK([1]اضافات!N46)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" t="str">
+        <f>HYPERLINK([1]اضافات!M46)</f>
+        <v>0</v>
+      </c>
+      <c r="G46" t="str">
+        <f>HYPERLINK([1]اضافات!F46)</f>
+        <v>0</v>
+      </c>
+      <c r="H46" t="str">
+        <f>HYPERLINK([1]اضافات!O46)</f>
+        <v>0</v>
+      </c>
+      <c r="I46" t="str">
+        <f>HYPERLINK([1]خصومات!L46)</f>
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>13</v>
       </c>
@@ -1899,8 +5315,36 @@
       <c r="D47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47" t="str">
+        <f>HYPERLINK([1]اضافات!N47)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" t="str">
+        <f>HYPERLINK([1]اضافات!M47)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" t="str">
+        <f>HYPERLINK([1]اضافات!F47)</f>
+        <v>0</v>
+      </c>
+      <c r="H47" t="str">
+        <f>HYPERLINK([1]اضافات!O47)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" t="str">
+        <f>HYPERLINK([1]خصومات!L47)</f>
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>14</v>
       </c>
@@ -1910,8 +5354,36 @@
       <c r="D48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48" t="str">
+        <f>HYPERLINK([1]اضافات!N48)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" t="str">
+        <f>HYPERLINK([1]اضافات!M48)</f>
+        <v>0</v>
+      </c>
+      <c r="G48" t="str">
+        <f>HYPERLINK([1]اضافات!F48)</f>
+        <v>0</v>
+      </c>
+      <c r="H48" t="str">
+        <f>HYPERLINK([1]اضافات!O48)</f>
+        <v>0</v>
+      </c>
+      <c r="I48" t="str">
+        <f>HYPERLINK([1]خصومات!L48)</f>
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>15</v>
       </c>
@@ -1921,56 +5393,252 @@
       <c r="D49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E49" t="str">
+        <f>HYPERLINK([1]اضافات!N49)</f>
+        <v>0</v>
+      </c>
+      <c r="F49" t="str">
+        <f>HYPERLINK([1]اضافات!M49)</f>
+        <v>0</v>
+      </c>
+      <c r="G49" t="str">
+        <f>HYPERLINK([1]اضافات!F49)</f>
+        <v>0</v>
+      </c>
+      <c r="H49" t="str">
+        <f>HYPERLINK([1]اضافات!O49)</f>
+        <v>0</v>
+      </c>
+      <c r="I49" t="str">
+        <f>HYPERLINK([1]خصومات!L49)</f>
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>9</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E50" t="str">
+        <f>HYPERLINK([1]اضافات!N50)</f>
+        <v>0</v>
+      </c>
+      <c r="F50" t="str">
+        <f>HYPERLINK([1]اضافات!M50)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" t="str">
+        <f>HYPERLINK([1]اضافات!F50)</f>
+        <v>0</v>
+      </c>
+      <c r="H50" t="str">
+        <f>HYPERLINK([1]اضافات!O50)</f>
+        <v>0</v>
+      </c>
+      <c r="I50" t="str">
+        <f>HYPERLINK([1]خصومات!L50)</f>
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>9</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E51" t="str">
+        <f>HYPERLINK([1]اضافات!N51)</f>
+        <v>0</v>
+      </c>
+      <c r="F51" t="str">
+        <f>HYPERLINK([1]اضافات!M51)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" t="str">
+        <f>HYPERLINK([1]اضافات!F51)</f>
+        <v>0</v>
+      </c>
+      <c r="H51" t="str">
+        <f>HYPERLINK([1]اضافات!O51)</f>
+        <v>0</v>
+      </c>
+      <c r="I51" t="str">
+        <f>HYPERLINK([1]خصومات!L51)</f>
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>9</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E52" t="str">
+        <f>HYPERLINK([1]اضافات!N52)</f>
+        <v>0</v>
+      </c>
+      <c r="F52" t="str">
+        <f>HYPERLINK([1]اضافات!M52)</f>
+        <v>0</v>
+      </c>
+      <c r="G52" t="str">
+        <f>HYPERLINK([1]اضافات!F52)</f>
+        <v>0</v>
+      </c>
+      <c r="H52" t="str">
+        <f>HYPERLINK([1]اضافات!O52)</f>
+        <v>0</v>
+      </c>
+      <c r="I52" t="str">
+        <f>HYPERLINK([1]خصومات!L52)</f>
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>9</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E53" t="str">
+        <f>HYPERLINK([1]اضافات!N53)</f>
+        <v>0</v>
+      </c>
+      <c r="F53" t="str">
+        <f>HYPERLINK([1]اضافات!M53)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" t="str">
+        <f>HYPERLINK([1]اضافات!F53)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" t="str">
+        <f>HYPERLINK([1]اضافات!O53)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" t="str">
+        <f>HYPERLINK([1]خصومات!L53)</f>
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>9</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E54" t="str">
+        <f>HYPERLINK([1]اضافات!N54)</f>
+        <v>0</v>
+      </c>
+      <c r="F54" t="str">
+        <f>HYPERLINK([1]اضافات!M54)</f>
+        <v>0</v>
+      </c>
+      <c r="G54" t="str">
+        <f>HYPERLINK([1]اضافات!F54)</f>
+        <v>0</v>
+      </c>
+      <c r="H54" t="str">
+        <f>HYPERLINK([1]اضافات!O54)</f>
+        <v>0</v>
+      </c>
+      <c r="I54" t="str">
+        <f>HYPERLINK([1]خصومات!L54)</f>
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>9</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E55" t="str">
+        <f>HYPERLINK([1]اضافات!N55)</f>
+        <v>0</v>
+      </c>
+      <c r="F55" t="str">
+        <f>HYPERLINK([1]اضافات!M55)</f>
+        <v>0</v>
+      </c>
+      <c r="G55" t="str">
+        <f>HYPERLINK([1]اضافات!F55)</f>
+        <v>0</v>
+      </c>
+      <c r="H55" t="str">
+        <f>HYPERLINK([1]اضافات!O55)</f>
+        <v>0</v>
+      </c>
+      <c r="I55" t="str">
+        <f>HYPERLINK([1]خصومات!L55)</f>
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>15</v>
       </c>
@@ -1981,8 +5649,40 @@
         <f>SUM(D19:D55)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E56">
+        <f t="shared" ref="E56:K56" si="3">SUM(E19:E55)</f>
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <f>SUM(K19:K55)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1</v>
       </c>
@@ -1992,8 +5692,36 @@
       <c r="D57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E57" t="str">
+        <f>HYPERLINK([1]اضافات!N57)</f>
+        <v>0</v>
+      </c>
+      <c r="F57" t="str">
+        <f>HYPERLINK([1]اضافات!M57)</f>
+        <v>0</v>
+      </c>
+      <c r="G57" t="str">
+        <f>HYPERLINK([1]اضافات!F57)</f>
+        <v>0</v>
+      </c>
+      <c r="H57" t="str">
+        <f>HYPERLINK([1]اضافات!O57)</f>
+        <v>0</v>
+      </c>
+      <c r="I57" t="str">
+        <f>HYPERLINK([1]خصومات!L57)</f>
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2</v>
       </c>
@@ -2003,32 +5731,144 @@
       <c r="D58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E58" t="str">
+        <f>HYPERLINK([1]اضافات!N58)</f>
+        <v>0</v>
+      </c>
+      <c r="F58" t="str">
+        <f>HYPERLINK([1]اضافات!M58)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" t="str">
+        <f>HYPERLINK([1]اضافات!F58)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" t="str">
+        <f>HYPERLINK([1]اضافات!O58)</f>
+        <v>0</v>
+      </c>
+      <c r="I58" t="str">
+        <f>HYPERLINK([1]خصومات!L58)</f>
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>29</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E59" t="str">
+        <f>HYPERLINK([1]اضافات!N59)</f>
+        <v>0</v>
+      </c>
+      <c r="F59" t="str">
+        <f>HYPERLINK([1]اضافات!M59)</f>
+        <v>0</v>
+      </c>
+      <c r="G59" t="str">
+        <f>HYPERLINK([1]اضافات!F59)</f>
+        <v>0</v>
+      </c>
+      <c r="H59" t="str">
+        <f>HYPERLINK([1]اضافات!O59)</f>
+        <v>0</v>
+      </c>
+      <c r="I59" t="str">
+        <f>HYPERLINK([1]خصومات!L59)</f>
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>29</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E60" t="str">
+        <f>HYPERLINK([1]اضافات!N60)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" t="str">
+        <f>HYPERLINK([1]اضافات!M60)</f>
+        <v>0</v>
+      </c>
+      <c r="G60" t="str">
+        <f>HYPERLINK([1]اضافات!F60)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" t="str">
+        <f>HYPERLINK([1]اضافات!O60)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" t="str">
+        <f>HYPERLINK([1]خصومات!L60)</f>
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>29</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E61" t="str">
+        <f>HYPERLINK([1]اضافات!N61)</f>
+        <v>0</v>
+      </c>
+      <c r="F61" t="str">
+        <f>HYPERLINK([1]اضافات!M61)</f>
+        <v>0</v>
+      </c>
+      <c r="G61" t="str">
+        <f>HYPERLINK([1]اضافات!F61)</f>
+        <v>0</v>
+      </c>
+      <c r="H61" t="str">
+        <f>HYPERLINK([1]اضافات!O61)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" t="str">
+        <f>HYPERLINK([1]خصومات!L61)</f>
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>3</v>
       </c>
@@ -2038,8 +5878,36 @@
       <c r="D62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E62" t="str">
+        <f>HYPERLINK([1]اضافات!N62)</f>
+        <v>0</v>
+      </c>
+      <c r="F62" t="str">
+        <f>HYPERLINK([1]اضافات!M62)</f>
+        <v>0</v>
+      </c>
+      <c r="G62" t="str">
+        <f>HYPERLINK([1]اضافات!F62)</f>
+        <v>0</v>
+      </c>
+      <c r="H62" t="str">
+        <f>HYPERLINK([1]اضافات!O62)</f>
+        <v>0</v>
+      </c>
+      <c r="I62" t="str">
+        <f>HYPERLINK([1]خصومات!L62)</f>
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>4</v>
       </c>
@@ -2049,40 +5917,180 @@
       <c r="D63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E63" t="str">
+        <f>HYPERLINK([1]اضافات!N63)</f>
+        <v>0</v>
+      </c>
+      <c r="F63" t="str">
+        <f>HYPERLINK([1]اضافات!M63)</f>
+        <v>0</v>
+      </c>
+      <c r="G63" t="str">
+        <f>HYPERLINK([1]اضافات!F63)</f>
+        <v>0</v>
+      </c>
+      <c r="H63" t="str">
+        <f>HYPERLINK([1]اضافات!O63)</f>
+        <v>0</v>
+      </c>
+      <c r="I63" t="str">
+        <f>HYPERLINK([1]خصومات!L63)</f>
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>32</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E64" t="str">
+        <f>HYPERLINK([1]اضافات!N64)</f>
+        <v>0</v>
+      </c>
+      <c r="F64" t="str">
+        <f>HYPERLINK([1]اضافات!M64)</f>
+        <v>0</v>
+      </c>
+      <c r="G64" t="str">
+        <f>HYPERLINK([1]اضافات!F64)</f>
+        <v>0</v>
+      </c>
+      <c r="H64" t="str">
+        <f>HYPERLINK([1]اضافات!O64)</f>
+        <v>0</v>
+      </c>
+      <c r="I64" t="str">
+        <f>HYPERLINK([1]خصومات!L64)</f>
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>32</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E65" t="str">
+        <f>HYPERLINK([1]اضافات!N65)</f>
+        <v>0</v>
+      </c>
+      <c r="F65" t="str">
+        <f>HYPERLINK([1]اضافات!M65)</f>
+        <v>0</v>
+      </c>
+      <c r="G65" t="str">
+        <f>HYPERLINK([1]اضافات!F65)</f>
+        <v>0</v>
+      </c>
+      <c r="H65" t="str">
+        <f>HYPERLINK([1]اضافات!O65)</f>
+        <v>0</v>
+      </c>
+      <c r="I65" t="str">
+        <f>HYPERLINK([1]خصومات!L65)</f>
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>32</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E66" t="str">
+        <f>HYPERLINK([1]اضافات!N66)</f>
+        <v>0</v>
+      </c>
+      <c r="F66" t="str">
+        <f>HYPERLINK([1]اضافات!M66)</f>
+        <v>0</v>
+      </c>
+      <c r="G66" t="str">
+        <f>HYPERLINK([1]اضافات!F66)</f>
+        <v>0</v>
+      </c>
+      <c r="H66" t="str">
+        <f>HYPERLINK([1]اضافات!O66)</f>
+        <v>0</v>
+      </c>
+      <c r="I66" t="str">
+        <f>HYPERLINK([1]خصومات!L66)</f>
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>32</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E67" t="str">
+        <f>HYPERLINK([1]اضافات!N67)</f>
+        <v>0</v>
+      </c>
+      <c r="F67" t="str">
+        <f>HYPERLINK([1]اضافات!M67)</f>
+        <v>0</v>
+      </c>
+      <c r="G67" t="str">
+        <f>HYPERLINK([1]اضافات!F67)</f>
+        <v>0</v>
+      </c>
+      <c r="H67" t="str">
+        <f>HYPERLINK([1]اضافات!O67)</f>
+        <v>0</v>
+      </c>
+      <c r="I67" t="str">
+        <f>HYPERLINK([1]خصومات!L67)</f>
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>5</v>
       </c>
@@ -2092,8 +6100,36 @@
       <c r="D68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E68" t="str">
+        <f>HYPERLINK([1]اضافات!N68)</f>
+        <v>0</v>
+      </c>
+      <c r="F68" t="str">
+        <f>HYPERLINK([1]اضافات!M68)</f>
+        <v>0</v>
+      </c>
+      <c r="G68" t="str">
+        <f>HYPERLINK([1]اضافات!F68)</f>
+        <v>0</v>
+      </c>
+      <c r="H68" t="str">
+        <f>HYPERLINK([1]اضافات!O68)</f>
+        <v>0</v>
+      </c>
+      <c r="I68" t="str">
+        <f>HYPERLINK([1]خصومات!L68)</f>
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>6</v>
       </c>
@@ -2103,8 +6139,36 @@
       <c r="D69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E69" t="str">
+        <f>HYPERLINK([1]اضافات!N69)</f>
+        <v>0</v>
+      </c>
+      <c r="F69" t="str">
+        <f>HYPERLINK([1]اضافات!M69)</f>
+        <v>0</v>
+      </c>
+      <c r="G69" t="str">
+        <f>HYPERLINK([1]اضافات!F69)</f>
+        <v>0</v>
+      </c>
+      <c r="H69" t="str">
+        <f>HYPERLINK([1]اضافات!O69)</f>
+        <v>0</v>
+      </c>
+      <c r="I69" t="str">
+        <f>HYPERLINK([1]خصومات!L69)</f>
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ref="J69:J117" si="4">SUM(D69,VALUE(E69),VALUE(F69),VALUE(G69))</f>
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ref="K69:K100" si="5">VALUE(D69)+VALUE(G69)+VALUE(H69)-VALUE(I69)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>0</v>
       </c>
@@ -2114,8 +6178,36 @@
       <c r="D70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E70" t="str">
+        <f>HYPERLINK([1]اضافات!N70)</f>
+        <v>0</v>
+      </c>
+      <c r="F70" t="str">
+        <f>HYPERLINK([1]اضافات!M70)</f>
+        <v>0</v>
+      </c>
+      <c r="G70" t="str">
+        <f>HYPERLINK([1]اضافات!F70)</f>
+        <v>0</v>
+      </c>
+      <c r="H70" t="str">
+        <f>HYPERLINK([1]اضافات!O70)</f>
+        <v>0</v>
+      </c>
+      <c r="I70" t="str">
+        <f>HYPERLINK([1]خصومات!L70)</f>
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>7</v>
       </c>
@@ -2125,8 +6217,36 @@
       <c r="D71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E71" t="str">
+        <f>HYPERLINK([1]اضافات!N71)</f>
+        <v>0</v>
+      </c>
+      <c r="F71" t="str">
+        <f>HYPERLINK([1]اضافات!M71)</f>
+        <v>0</v>
+      </c>
+      <c r="G71" t="str">
+        <f>HYPERLINK([1]اضافات!F71)</f>
+        <v>0</v>
+      </c>
+      <c r="H71" t="str">
+        <f>HYPERLINK([1]اضافات!O71)</f>
+        <v>0</v>
+      </c>
+      <c r="I71" t="str">
+        <f>HYPERLINK([1]خصومات!L71)</f>
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>8</v>
       </c>
@@ -2136,8 +6256,36 @@
       <c r="D72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E72" t="str">
+        <f>HYPERLINK([1]اضافات!N72)</f>
+        <v>0</v>
+      </c>
+      <c r="F72" t="str">
+        <f>HYPERLINK([1]اضافات!M72)</f>
+        <v>0</v>
+      </c>
+      <c r="G72" t="str">
+        <f>HYPERLINK([1]اضافات!F72)</f>
+        <v>0</v>
+      </c>
+      <c r="H72" t="str">
+        <f>HYPERLINK([1]اضافات!O72)</f>
+        <v>0</v>
+      </c>
+      <c r="I72" t="str">
+        <f>HYPERLINK([1]خصومات!L72)</f>
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>9</v>
       </c>
@@ -2147,8 +6295,36 @@
       <c r="D73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E73" t="str">
+        <f>HYPERLINK([1]اضافات!N73)</f>
+        <v>0</v>
+      </c>
+      <c r="F73" t="str">
+        <f>HYPERLINK([1]اضافات!M73)</f>
+        <v>0</v>
+      </c>
+      <c r="G73" t="str">
+        <f>HYPERLINK([1]اضافات!F73)</f>
+        <v>0</v>
+      </c>
+      <c r="H73" t="str">
+        <f>HYPERLINK([1]اضافات!O73)</f>
+        <v>0</v>
+      </c>
+      <c r="I73" t="str">
+        <f>HYPERLINK([1]خصومات!L73)</f>
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>10</v>
       </c>
@@ -2158,8 +6334,36 @@
       <c r="D74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E74" t="str">
+        <f>HYPERLINK([1]اضافات!N74)</f>
+        <v>0</v>
+      </c>
+      <c r="F74" t="str">
+        <f>HYPERLINK([1]اضافات!M74)</f>
+        <v>0</v>
+      </c>
+      <c r="G74" t="str">
+        <f>HYPERLINK([1]اضافات!F74)</f>
+        <v>0</v>
+      </c>
+      <c r="H74" t="str">
+        <f>HYPERLINK([1]اضافات!O74)</f>
+        <v>0</v>
+      </c>
+      <c r="I74" t="str">
+        <f>HYPERLINK([1]خصومات!L74)</f>
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>11</v>
       </c>
@@ -2169,8 +6373,36 @@
       <c r="D75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E75" t="str">
+        <f>HYPERLINK([1]اضافات!N75)</f>
+        <v>0</v>
+      </c>
+      <c r="F75" t="str">
+        <f>HYPERLINK([1]اضافات!M75)</f>
+        <v>0</v>
+      </c>
+      <c r="G75" t="str">
+        <f>HYPERLINK([1]اضافات!F75)</f>
+        <v>0</v>
+      </c>
+      <c r="H75" t="str">
+        <f>HYPERLINK([1]اضافات!O75)</f>
+        <v>0</v>
+      </c>
+      <c r="I75" t="str">
+        <f>HYPERLINK([1]خصومات!L75)</f>
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>12</v>
       </c>
@@ -2180,8 +6412,36 @@
       <c r="D76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E76" t="str">
+        <f>HYPERLINK([1]اضافات!N76)</f>
+        <v>0</v>
+      </c>
+      <c r="F76" t="str">
+        <f>HYPERLINK([1]اضافات!M76)</f>
+        <v>0</v>
+      </c>
+      <c r="G76" t="str">
+        <f>HYPERLINK([1]اضافات!F76)</f>
+        <v>0</v>
+      </c>
+      <c r="H76" t="str">
+        <f>HYPERLINK([1]اضافات!O76)</f>
+        <v>0</v>
+      </c>
+      <c r="I76" t="str">
+        <f>HYPERLINK([1]خصومات!L76)</f>
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>13</v>
       </c>
@@ -2191,8 +6451,36 @@
       <c r="D77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E77" t="str">
+        <f>HYPERLINK([1]اضافات!N77)</f>
+        <v>0</v>
+      </c>
+      <c r="F77" t="str">
+        <f>HYPERLINK([1]اضافات!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="G77" t="str">
+        <f>HYPERLINK([1]اضافات!F77)</f>
+        <v>0</v>
+      </c>
+      <c r="H77" t="str">
+        <f>HYPERLINK([1]اضافات!O77)</f>
+        <v>0</v>
+      </c>
+      <c r="I77" t="str">
+        <f>HYPERLINK([1]خصومات!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>14</v>
       </c>
@@ -2202,8 +6490,36 @@
       <c r="D78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E78" t="str">
+        <f>HYPERLINK([1]اضافات!N78)</f>
+        <v>0</v>
+      </c>
+      <c r="F78" t="str">
+        <f>HYPERLINK([1]اضافات!M78)</f>
+        <v>0</v>
+      </c>
+      <c r="G78" t="str">
+        <f>HYPERLINK([1]اضافات!F78)</f>
+        <v>0</v>
+      </c>
+      <c r="H78" t="str">
+        <f>HYPERLINK([1]اضافات!O78)</f>
+        <v>0</v>
+      </c>
+      <c r="I78" t="str">
+        <f>HYPERLINK([1]خصومات!L78)</f>
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>15</v>
       </c>
@@ -2213,16 +6529,72 @@
       <c r="D79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E79" t="str">
+        <f>HYPERLINK([1]اضافات!N79)</f>
+        <v>0</v>
+      </c>
+      <c r="F79" t="str">
+        <f>HYPERLINK([1]اضافات!M79)</f>
+        <v>0</v>
+      </c>
+      <c r="G79" t="str">
+        <f>HYPERLINK([1]اضافات!F79)</f>
+        <v>0</v>
+      </c>
+      <c r="H79" t="str">
+        <f>HYPERLINK([1]اضافات!O79)</f>
+        <v>0</v>
+      </c>
+      <c r="I79" t="str">
+        <f>HYPERLINK([1]خصومات!L79)</f>
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>0</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E80" t="str">
+        <f>HYPERLINK([1]اضافات!N80)</f>
+        <v>0</v>
+      </c>
+      <c r="F80" t="str">
+        <f>HYPERLINK([1]اضافات!M80)</f>
+        <v>0</v>
+      </c>
+      <c r="G80" t="str">
+        <f>HYPERLINK([1]اضافات!F80)</f>
+        <v>0</v>
+      </c>
+      <c r="H80" t="str">
+        <f>HYPERLINK([1]اضافات!O80)</f>
+        <v>0</v>
+      </c>
+      <c r="I80" t="str">
+        <f>HYPERLINK([1]خصومات!L80)</f>
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>16</v>
       </c>
@@ -2232,8 +6604,36 @@
       <c r="D81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E81" t="str">
+        <f>HYPERLINK([1]اضافات!N81)</f>
+        <v>0</v>
+      </c>
+      <c r="F81" t="str">
+        <f>HYPERLINK([1]اضافات!M81)</f>
+        <v>0</v>
+      </c>
+      <c r="G81" t="str">
+        <f>HYPERLINK([1]اضافات!F81)</f>
+        <v>0</v>
+      </c>
+      <c r="H81" t="str">
+        <f>HYPERLINK([1]اضافات!O81)</f>
+        <v>0</v>
+      </c>
+      <c r="I81" t="str">
+        <f>HYPERLINK([1]خصومات!L81)</f>
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>17</v>
       </c>
@@ -2243,8 +6643,36 @@
       <c r="D82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E82" t="str">
+        <f>HYPERLINK([1]اضافات!N82)</f>
+        <v>0</v>
+      </c>
+      <c r="F82" t="str">
+        <f>HYPERLINK([1]اضافات!M82)</f>
+        <v>0</v>
+      </c>
+      <c r="G82" t="str">
+        <f>HYPERLINK([1]اضافات!F82)</f>
+        <v>0</v>
+      </c>
+      <c r="H82" t="str">
+        <f>HYPERLINK([1]اضافات!O82)</f>
+        <v>0</v>
+      </c>
+      <c r="I82" t="str">
+        <f>HYPERLINK([1]خصومات!L82)</f>
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>18</v>
       </c>
@@ -2254,8 +6682,36 @@
       <c r="D83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E83" t="str">
+        <f>HYPERLINK([1]اضافات!N83)</f>
+        <v>0</v>
+      </c>
+      <c r="F83" t="str">
+        <f>HYPERLINK([1]اضافات!M83)</f>
+        <v>0</v>
+      </c>
+      <c r="G83" t="str">
+        <f>HYPERLINK([1]اضافات!F83)</f>
+        <v>0</v>
+      </c>
+      <c r="H83" t="str">
+        <f>HYPERLINK([1]اضافات!O83)</f>
+        <v>0</v>
+      </c>
+      <c r="I83" t="str">
+        <f>HYPERLINK([1]خصومات!L83)</f>
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>19</v>
       </c>
@@ -2265,8 +6721,36 @@
       <c r="D84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E84" t="str">
+        <f>HYPERLINK([1]اضافات!N84)</f>
+        <v>0</v>
+      </c>
+      <c r="F84" t="str">
+        <f>HYPERLINK([1]اضافات!M84)</f>
+        <v>0</v>
+      </c>
+      <c r="G84" t="str">
+        <f>HYPERLINK([1]اضافات!F84)</f>
+        <v>0</v>
+      </c>
+      <c r="H84" t="str">
+        <f>HYPERLINK([1]اضافات!O84)</f>
+        <v>0</v>
+      </c>
+      <c r="I84" t="str">
+        <f>HYPERLINK([1]خصومات!L84)</f>
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>20</v>
       </c>
@@ -2276,128 +6760,576 @@
       <c r="D85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E85" t="str">
+        <f>HYPERLINK([1]اضافات!N85)</f>
+        <v>0</v>
+      </c>
+      <c r="F85" t="str">
+        <f>HYPERLINK([1]اضافات!M85)</f>
+        <v>0</v>
+      </c>
+      <c r="G85" t="str">
+        <f>HYPERLINK([1]اضافات!F85)</f>
+        <v>0</v>
+      </c>
+      <c r="H85" t="str">
+        <f>HYPERLINK([1]اضافات!O85)</f>
+        <v>0</v>
+      </c>
+      <c r="I85" t="str">
+        <f>HYPERLINK([1]خصومات!L85)</f>
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>9</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E86" t="str">
+        <f>HYPERLINK([1]اضافات!N86)</f>
+        <v>0</v>
+      </c>
+      <c r="F86" t="str">
+        <f>HYPERLINK([1]اضافات!M86)</f>
+        <v>0</v>
+      </c>
+      <c r="G86" t="str">
+        <f>HYPERLINK([1]اضافات!F86)</f>
+        <v>0</v>
+      </c>
+      <c r="H86" t="str">
+        <f>HYPERLINK([1]اضافات!O86)</f>
+        <v>0</v>
+      </c>
+      <c r="I86" t="str">
+        <f>HYPERLINK([1]خصومات!L86)</f>
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
         <v>9</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E87" t="str">
+        <f>HYPERLINK([1]اضافات!N87)</f>
+        <v>0</v>
+      </c>
+      <c r="F87" t="str">
+        <f>HYPERLINK([1]اضافات!M87)</f>
+        <v>0</v>
+      </c>
+      <c r="G87" t="str">
+        <f>HYPERLINK([1]اضافات!F87)</f>
+        <v>0</v>
+      </c>
+      <c r="H87" t="str">
+        <f>HYPERLINK([1]اضافات!O87)</f>
+        <v>0</v>
+      </c>
+      <c r="I87" t="str">
+        <f>HYPERLINK([1]خصومات!L87)</f>
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>9</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E88" t="str">
+        <f>HYPERLINK([1]اضافات!N88)</f>
+        <v>0</v>
+      </c>
+      <c r="F88" t="str">
+        <f>HYPERLINK([1]اضافات!M88)</f>
+        <v>0</v>
+      </c>
+      <c r="G88" t="str">
+        <f>HYPERLINK([1]اضافات!F88)</f>
+        <v>0</v>
+      </c>
+      <c r="H88" t="str">
+        <f>HYPERLINK([1]اضافات!O88)</f>
+        <v>0</v>
+      </c>
+      <c r="I88" t="str">
+        <f>HYPERLINK([1]خصومات!L88)</f>
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>9</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E89" t="str">
+        <f>HYPERLINK([1]اضافات!N89)</f>
+        <v>0</v>
+      </c>
+      <c r="F89" t="str">
+        <f>HYPERLINK([1]اضافات!M89)</f>
+        <v>0</v>
+      </c>
+      <c r="G89" t="str">
+        <f>HYPERLINK([1]اضافات!F89)</f>
+        <v>0</v>
+      </c>
+      <c r="H89" t="str">
+        <f>HYPERLINK([1]اضافات!O89)</f>
+        <v>0</v>
+      </c>
+      <c r="I89" t="str">
+        <f>HYPERLINK([1]خصومات!L89)</f>
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>9</v>
       </c>
       <c r="D90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E90" t="str">
+        <f>HYPERLINK([1]اضافات!N90)</f>
+        <v>0</v>
+      </c>
+      <c r="F90" t="str">
+        <f>HYPERLINK([1]اضافات!M90)</f>
+        <v>0</v>
+      </c>
+      <c r="G90" t="str">
+        <f>HYPERLINK([1]اضافات!F90)</f>
+        <v>0</v>
+      </c>
+      <c r="H90" t="str">
+        <f>HYPERLINK([1]اضافات!O90)</f>
+        <v>0</v>
+      </c>
+      <c r="I90" t="str">
+        <f>HYPERLINK([1]خصومات!L90)</f>
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>9</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E91" t="str">
+        <f>HYPERLINK([1]اضافات!N91)</f>
+        <v>0</v>
+      </c>
+      <c r="F91" t="str">
+        <f>HYPERLINK([1]اضافات!M91)</f>
+        <v>0</v>
+      </c>
+      <c r="G91" t="str">
+        <f>HYPERLINK([1]اضافات!F91)</f>
+        <v>0</v>
+      </c>
+      <c r="H91" t="str">
+        <f>HYPERLINK([1]اضافات!O91)</f>
+        <v>0</v>
+      </c>
+      <c r="I91" t="str">
+        <f>HYPERLINK([1]خصومات!L91)</f>
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>9</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E92" t="str">
+        <f>HYPERLINK([1]اضافات!N92)</f>
+        <v>0</v>
+      </c>
+      <c r="F92" t="str">
+        <f>HYPERLINK([1]اضافات!M92)</f>
+        <v>0</v>
+      </c>
+      <c r="G92" t="str">
+        <f>HYPERLINK([1]اضافات!F92)</f>
+        <v>0</v>
+      </c>
+      <c r="H92" t="str">
+        <f>HYPERLINK([1]اضافات!O92)</f>
+        <v>0</v>
+      </c>
+      <c r="I92" t="str">
+        <f>HYPERLINK([1]خصومات!L92)</f>
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
         <v>9</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E93" t="str">
+        <f>HYPERLINK([1]اضافات!N93)</f>
+        <v>0</v>
+      </c>
+      <c r="F93" t="str">
+        <f>HYPERLINK([1]اضافات!M93)</f>
+        <v>0</v>
+      </c>
+      <c r="G93" t="str">
+        <f>HYPERLINK([1]اضافات!F93)</f>
+        <v>0</v>
+      </c>
+      <c r="H93" t="str">
+        <f>HYPERLINK([1]اضافات!O93)</f>
+        <v>0</v>
+      </c>
+      <c r="I93" t="str">
+        <f>HYPERLINK([1]خصومات!L93)</f>
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>9</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E94" t="str">
+        <f>HYPERLINK([1]اضافات!N94)</f>
+        <v>0</v>
+      </c>
+      <c r="F94" t="str">
+        <f>HYPERLINK([1]اضافات!M94)</f>
+        <v>0</v>
+      </c>
+      <c r="G94" t="str">
+        <f>HYPERLINK([1]اضافات!F94)</f>
+        <v>0</v>
+      </c>
+      <c r="H94" t="str">
+        <f>HYPERLINK([1]اضافات!O94)</f>
+        <v>0</v>
+      </c>
+      <c r="I94" t="str">
+        <f>HYPERLINK([1]خصومات!L94)</f>
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>9</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E95" t="str">
+        <f>HYPERLINK([1]اضافات!N95)</f>
+        <v>0</v>
+      </c>
+      <c r="F95" t="str">
+        <f>HYPERLINK([1]اضافات!M95)</f>
+        <v>0</v>
+      </c>
+      <c r="G95" t="str">
+        <f>HYPERLINK([1]اضافات!F95)</f>
+        <v>0</v>
+      </c>
+      <c r="H95" t="str">
+        <f>HYPERLINK([1]اضافات!O95)</f>
+        <v>0</v>
+      </c>
+      <c r="I95" t="str">
+        <f>HYPERLINK([1]خصومات!L95)</f>
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>9</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E96" t="str">
+        <f>HYPERLINK([1]اضافات!N96)</f>
+        <v>0</v>
+      </c>
+      <c r="F96" t="str">
+        <f>HYPERLINK([1]اضافات!M96)</f>
+        <v>0</v>
+      </c>
+      <c r="G96" t="str">
+        <f>HYPERLINK([1]اضافات!F96)</f>
+        <v>0</v>
+      </c>
+      <c r="H96" t="str">
+        <f>HYPERLINK([1]اضافات!O96)</f>
+        <v>0</v>
+      </c>
+      <c r="I96" t="str">
+        <f>HYPERLINK([1]خصومات!L96)</f>
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>9</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E97" t="str">
+        <f>HYPERLINK([1]اضافات!N97)</f>
+        <v>0</v>
+      </c>
+      <c r="F97" t="str">
+        <f>HYPERLINK([1]اضافات!M97)</f>
+        <v>0</v>
+      </c>
+      <c r="G97" t="str">
+        <f>HYPERLINK([1]اضافات!F97)</f>
+        <v>0</v>
+      </c>
+      <c r="H97" t="str">
+        <f>HYPERLINK([1]اضافات!O97)</f>
+        <v>0</v>
+      </c>
+      <c r="I97" t="str">
+        <f>HYPERLINK([1]خصومات!L97)</f>
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>9</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E98" t="str">
+        <f>HYPERLINK([1]اضافات!N98)</f>
+        <v>0</v>
+      </c>
+      <c r="F98" t="str">
+        <f>HYPERLINK([1]اضافات!M98)</f>
+        <v>0</v>
+      </c>
+      <c r="G98" t="str">
+        <f>HYPERLINK([1]اضافات!F98)</f>
+        <v>0</v>
+      </c>
+      <c r="H98" t="str">
+        <f>HYPERLINK([1]اضافات!O98)</f>
+        <v>0</v>
+      </c>
+      <c r="I98" t="str">
+        <f>HYPERLINK([1]خصومات!L98)</f>
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>9</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E99" t="str">
+        <f>HYPERLINK([1]اضافات!N99)</f>
+        <v>0</v>
+      </c>
+      <c r="F99" t="str">
+        <f>HYPERLINK([1]اضافات!M99)</f>
+        <v>0</v>
+      </c>
+      <c r="G99" t="str">
+        <f>HYPERLINK([1]اضافات!F99)</f>
+        <v>0</v>
+      </c>
+      <c r="H99" t="str">
+        <f>HYPERLINK([1]اضافات!O99)</f>
+        <v>0</v>
+      </c>
+      <c r="I99" t="str">
+        <f>HYPERLINK([1]خصومات!L99)</f>
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>9</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E100" t="str">
+        <f>HYPERLINK([1]اضافات!N100)</f>
+        <v>0</v>
+      </c>
+      <c r="F100" t="str">
+        <f>HYPERLINK([1]اضافات!M100)</f>
+        <v>0</v>
+      </c>
+      <c r="G100" t="str">
+        <f>HYPERLINK([1]اضافات!F100)</f>
+        <v>0</v>
+      </c>
+      <c r="H100" t="str">
+        <f>HYPERLINK([1]اضافات!O100)</f>
+        <v>0</v>
+      </c>
+      <c r="I100" t="str">
+        <f>HYPERLINK([1]خصومات!L100)</f>
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>20</v>
       </c>
@@ -2408,8 +7340,40 @@
         <f>SUM(D57:D100)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E101">
+        <f t="shared" ref="E101:K101" si="6">SUM(E57:E100)</f>
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <f>SUM(K57:K100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1</v>
       </c>
@@ -2419,8 +7383,36 @@
       <c r="D102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E102" t="str">
+        <f>HYPERLINK([1]اضافات!N102)</f>
+        <v>0</v>
+      </c>
+      <c r="F102" t="str">
+        <f>HYPERLINK([1]اضافات!M102)</f>
+        <v>0</v>
+      </c>
+      <c r="G102" t="str">
+        <f>HYPERLINK([1]اضافات!F102)</f>
+        <v>0</v>
+      </c>
+      <c r="H102" t="str">
+        <f>HYPERLINK([1]اضافات!O102)</f>
+        <v>0</v>
+      </c>
+      <c r="I102" t="str">
+        <f>HYPERLINK([1]خصومات!L102)</f>
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <f t="shared" ref="K102:K117" si="7">VALUE(D102)+VALUE(G102)+VALUE(H102)-VALUE(I102)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2</v>
       </c>
@@ -2430,8 +7422,36 @@
       <c r="D103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E103" t="str">
+        <f>HYPERLINK([1]اضافات!N103)</f>
+        <v>0</v>
+      </c>
+      <c r="F103" t="str">
+        <f>HYPERLINK([1]اضافات!M103)</f>
+        <v>0</v>
+      </c>
+      <c r="G103" t="str">
+        <f>HYPERLINK([1]اضافات!F103)</f>
+        <v>0</v>
+      </c>
+      <c r="H103" t="str">
+        <f>HYPERLINK([1]اضافات!O103)</f>
+        <v>0</v>
+      </c>
+      <c r="I103" t="str">
+        <f>HYPERLINK([1]خصومات!L103)</f>
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>3</v>
       </c>
@@ -2441,8 +7461,36 @@
       <c r="D104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E104" t="str">
+        <f>HYPERLINK([1]اضافات!N104)</f>
+        <v>0</v>
+      </c>
+      <c r="F104" t="str">
+        <f>HYPERLINK([1]اضافات!M104)</f>
+        <v>0</v>
+      </c>
+      <c r="G104" t="str">
+        <f>HYPERLINK([1]اضافات!F104)</f>
+        <v>0</v>
+      </c>
+      <c r="H104" t="str">
+        <f>HYPERLINK([1]اضافات!O104)</f>
+        <v>0</v>
+      </c>
+      <c r="I104" t="str">
+        <f>HYPERLINK([1]خصومات!L104)</f>
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>4</v>
       </c>
@@ -2452,8 +7500,36 @@
       <c r="D105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E105" t="str">
+        <f>HYPERLINK([1]اضافات!N105)</f>
+        <v>0</v>
+      </c>
+      <c r="F105" t="str">
+        <f>HYPERLINK([1]اضافات!M105)</f>
+        <v>0</v>
+      </c>
+      <c r="G105" t="str">
+        <f>HYPERLINK([1]اضافات!F105)</f>
+        <v>0</v>
+      </c>
+      <c r="H105" t="str">
+        <f>HYPERLINK([1]اضافات!O105)</f>
+        <v>0</v>
+      </c>
+      <c r="I105" t="str">
+        <f>HYPERLINK([1]خصومات!L105)</f>
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>5</v>
       </c>
@@ -2463,8 +7539,36 @@
       <c r="D106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E106" t="str">
+        <f>HYPERLINK([1]اضافات!N106)</f>
+        <v>0</v>
+      </c>
+      <c r="F106" t="str">
+        <f>HYPERLINK([1]اضافات!M106)</f>
+        <v>0</v>
+      </c>
+      <c r="G106" t="str">
+        <f>HYPERLINK([1]اضافات!F106)</f>
+        <v>0</v>
+      </c>
+      <c r="H106" t="str">
+        <f>HYPERLINK([1]اضافات!O106)</f>
+        <v>0</v>
+      </c>
+      <c r="I106" t="str">
+        <f>HYPERLINK([1]خصومات!L106)</f>
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>6</v>
       </c>
@@ -2474,8 +7578,36 @@
       <c r="D107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E107" t="str">
+        <f>HYPERLINK([1]اضافات!N107)</f>
+        <v>0</v>
+      </c>
+      <c r="F107" t="str">
+        <f>HYPERLINK([1]اضافات!M107)</f>
+        <v>0</v>
+      </c>
+      <c r="G107" t="str">
+        <f>HYPERLINK([1]اضافات!F107)</f>
+        <v>0</v>
+      </c>
+      <c r="H107" t="str">
+        <f>HYPERLINK([1]اضافات!O107)</f>
+        <v>0</v>
+      </c>
+      <c r="I107" t="str">
+        <f>HYPERLINK([1]خصومات!L107)</f>
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>7</v>
       </c>
@@ -2485,80 +7617,360 @@
       <c r="D108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E108" t="str">
+        <f>HYPERLINK([1]اضافات!N108)</f>
+        <v>0</v>
+      </c>
+      <c r="F108" t="str">
+        <f>HYPERLINK([1]اضافات!M108)</f>
+        <v>0</v>
+      </c>
+      <c r="G108" t="str">
+        <f>HYPERLINK([1]اضافات!F108)</f>
+        <v>0</v>
+      </c>
+      <c r="H108" t="str">
+        <f>HYPERLINK([1]اضافات!O108)</f>
+        <v>0</v>
+      </c>
+      <c r="I108" t="str">
+        <f>HYPERLINK([1]خصومات!L108)</f>
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>9</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E109" t="str">
+        <f>HYPERLINK([1]اضافات!N109)</f>
+        <v>0</v>
+      </c>
+      <c r="F109" t="str">
+        <f>HYPERLINK([1]اضافات!M109)</f>
+        <v>0</v>
+      </c>
+      <c r="G109" t="str">
+        <f>HYPERLINK([1]اضافات!F109)</f>
+        <v>0</v>
+      </c>
+      <c r="H109" t="str">
+        <f>HYPERLINK([1]اضافات!O109)</f>
+        <v>0</v>
+      </c>
+      <c r="I109" t="str">
+        <f>HYPERLINK([1]خصومات!L109)</f>
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>9</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E110" t="str">
+        <f>HYPERLINK([1]اضافات!N110)</f>
+        <v>0</v>
+      </c>
+      <c r="F110" t="str">
+        <f>HYPERLINK([1]اضافات!M110)</f>
+        <v>0</v>
+      </c>
+      <c r="G110" t="str">
+        <f>HYPERLINK([1]اضافات!F110)</f>
+        <v>0</v>
+      </c>
+      <c r="H110" t="str">
+        <f>HYPERLINK([1]اضافات!O110)</f>
+        <v>0</v>
+      </c>
+      <c r="I110" t="str">
+        <f>HYPERLINK([1]خصومات!L110)</f>
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>9</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E111" t="str">
+        <f>HYPERLINK([1]اضافات!N111)</f>
+        <v>0</v>
+      </c>
+      <c r="F111" t="str">
+        <f>HYPERLINK([1]اضافات!M111)</f>
+        <v>0</v>
+      </c>
+      <c r="G111" t="str">
+        <f>HYPERLINK([1]اضافات!F111)</f>
+        <v>0</v>
+      </c>
+      <c r="H111" t="str">
+        <f>HYPERLINK([1]اضافات!O111)</f>
+        <v>0</v>
+      </c>
+      <c r="I111" t="str">
+        <f>HYPERLINK([1]خصومات!L111)</f>
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>9</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E112" t="str">
+        <f>HYPERLINK([1]اضافات!N112)</f>
+        <v>0</v>
+      </c>
+      <c r="F112" t="str">
+        <f>HYPERLINK([1]اضافات!M112)</f>
+        <v>0</v>
+      </c>
+      <c r="G112" t="str">
+        <f>HYPERLINK([1]اضافات!F112)</f>
+        <v>0</v>
+      </c>
+      <c r="H112" t="str">
+        <f>HYPERLINK([1]اضافات!O112)</f>
+        <v>0</v>
+      </c>
+      <c r="I112" t="str">
+        <f>HYPERLINK([1]خصومات!L112)</f>
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
         <v>9</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E113" t="str">
+        <f>HYPERLINK([1]اضافات!N113)</f>
+        <v>0</v>
+      </c>
+      <c r="F113" t="str">
+        <f>HYPERLINK([1]اضافات!M113)</f>
+        <v>0</v>
+      </c>
+      <c r="G113" t="str">
+        <f>HYPERLINK([1]اضافات!F113)</f>
+        <v>0</v>
+      </c>
+      <c r="H113" t="str">
+        <f>HYPERLINK([1]اضافات!O113)</f>
+        <v>0</v>
+      </c>
+      <c r="I113" t="str">
+        <f>HYPERLINK([1]خصومات!L113)</f>
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
         <v>9</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E114" t="str">
+        <f>HYPERLINK([1]اضافات!N114)</f>
+        <v>0</v>
+      </c>
+      <c r="F114" t="str">
+        <f>HYPERLINK([1]اضافات!M114)</f>
+        <v>0</v>
+      </c>
+      <c r="G114" t="str">
+        <f>HYPERLINK([1]اضافات!F114)</f>
+        <v>0</v>
+      </c>
+      <c r="H114" t="str">
+        <f>HYPERLINK([1]اضافات!O114)</f>
+        <v>0</v>
+      </c>
+      <c r="I114" t="str">
+        <f>HYPERLINK([1]خصومات!L114)</f>
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>9</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E115" t="str">
+        <f>HYPERLINK([1]اضافات!N115)</f>
+        <v>0</v>
+      </c>
+      <c r="F115" t="str">
+        <f>HYPERLINK([1]اضافات!M115)</f>
+        <v>0</v>
+      </c>
+      <c r="G115" t="str">
+        <f>HYPERLINK([1]اضافات!F115)</f>
+        <v>0</v>
+      </c>
+      <c r="H115" t="str">
+        <f>HYPERLINK([1]اضافات!O115)</f>
+        <v>0</v>
+      </c>
+      <c r="I115" t="str">
+        <f>HYPERLINK([1]خصومات!L115)</f>
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>9</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E116" t="str">
+        <f>HYPERLINK([1]اضافات!N116)</f>
+        <v>0</v>
+      </c>
+      <c r="F116" t="str">
+        <f>HYPERLINK([1]اضافات!M116)</f>
+        <v>0</v>
+      </c>
+      <c r="G116" t="str">
+        <f>HYPERLINK([1]اضافات!F116)</f>
+        <v>0</v>
+      </c>
+      <c r="H116" t="str">
+        <f>HYPERLINK([1]اضافات!O116)</f>
+        <v>0</v>
+      </c>
+      <c r="I116" t="str">
+        <f>HYPERLINK([1]خصومات!L116)</f>
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>9</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E117" t="str">
+        <f>HYPERLINK([1]اضافات!N117)</f>
+        <v>0</v>
+      </c>
+      <c r="F117" t="str">
+        <f>HYPERLINK([1]اضافات!M117)</f>
+        <v>0</v>
+      </c>
+      <c r="G117" t="str">
+        <f>HYPERLINK([1]اضافات!F117)</f>
+        <v>0</v>
+      </c>
+      <c r="H117" t="str">
+        <f>HYPERLINK([1]اضافات!O117)</f>
+        <v>0</v>
+      </c>
+      <c r="I117" t="str">
+        <f>HYPERLINK([1]خصومات!L117)</f>
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>6</v>
       </c>
@@ -2569,10 +7981,42 @@
         <f>SUM(D102:D117)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E118">
+        <f t="shared" ref="E118:K118" si="8">SUM(E102:E117)</f>
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <f>SUM(K102:K117)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119">
-        <f t="shared" ref="A119" si="0">SUM(A18,A56,A101)</f>
+        <f t="shared" ref="A119" si="9">SUM(A18,A56,A101)</f>
         <v>38</v>
       </c>
       <c r="B119" t="s">
@@ -2582,8 +8026,40 @@
         <f>SUM(D18,D56,D101)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E119">
+        <f t="shared" ref="E119:J119" si="10">SUM(E18,E56,E101)</f>
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <f>SUM(K18,K56,K101)</f>
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <f>SUM(L18,L56,L101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120">
         <f>SUM(A18,A56,A101,A118)</f>
         <v>44</v>
@@ -2592,7 +8068,39 @@
         <v>60</v>
       </c>
       <c r="D120">
-        <f t="shared" ref="D120" si="1">SUM(D18,D56,D101,D118)</f>
+        <f t="shared" ref="D120:K120" si="11">SUM(D18,D56,D101,D118)</f>
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <f>SUM(L18,L56,L101,L118)</f>
         <v>0</v>
       </c>
     </row>
@@ -2633,56 +8141,56 @@
       <c r="P1" s="44"/>
       <c r="Q1" s="44"/>
     </row>
-    <row r="2" spans="1:17" s="43" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+    <row r="2" spans="1:17" s="43" customFormat="1" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
         <v>62</v>
       </c>
       <c r="B2" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="45" t="s">
+      <c r="K2" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="45" t="s">
+      <c r="L2" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="45" t="s">
+      <c r="M2" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="45" t="s">
+      <c r="N2" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="45" t="s">
+      <c r="O2" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="45" t="s">
+      <c r="P2" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="45" t="s">
+      <c r="Q2" s="65" t="s">
         <v>78</v>
       </c>
     </row>
@@ -9179,50 +14687,55 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38BFDA8-BF74-4049-815A-1E798993C700}">
   <dimension ref="A1:M118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="13" width="20.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:13" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="65" t="s">
         <v>78</v>
       </c>
     </row>

--- a/Sheets/Salaries.xlsx
+++ b/Sheets/Salaries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\SalariesSummary\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C068724F-830D-467D-B7E0-158BC0E48612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B8DB1C-AC38-4714-9DAA-225C775653A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="مرتبات" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="177">
   <si>
     <t>ديسمبر 2025</t>
   </si>
@@ -67,9 +67,6 @@
     <t>أ/أميرة محمد على شريف</t>
   </si>
   <si>
-    <t>أ/إيهاب حمدى ابراهيم</t>
-  </si>
-  <si>
     <t>Spare</t>
   </si>
   <si>
@@ -79,76 +76,22 @@
     <t>أ/ناجى رمضان أمين محمد</t>
   </si>
   <si>
-    <t>أ/محمد عبد العزيز عبدالحافظ</t>
-  </si>
-  <si>
-    <t>أ/ أحمد سعيد أحمد محمد علي</t>
-  </si>
-  <si>
-    <t>أ/منة الله البلتاجى</t>
-  </si>
-  <si>
     <t>أ/نهى عمرو محمد رضوان</t>
-  </si>
-  <si>
-    <t>أ/عبد الله عمرو حافظ</t>
-  </si>
-  <si>
-    <t>أ/محمد حمدى كامل</t>
-  </si>
-  <si>
-    <t>أ/أحمد سيف الدين أبو بكر سري الدين</t>
-  </si>
-  <si>
-    <t>أ/هاني أحمد الدالي</t>
-  </si>
-  <si>
-    <t>أ/عبدالرحمن أحمد عبدالعزيز حسن</t>
-  </si>
-  <si>
-    <t>أ/حبيبة محمود سمير محمود عيسى</t>
-  </si>
-  <si>
-    <t>أ/احمد ابو العباس محمد الاتربي</t>
-  </si>
-  <si>
-    <t>أ/ليلي امين محمد امين طموم</t>
   </si>
   <si>
     <t>أ/كريم ايمن محمد عادل</t>
   </si>
   <si>
-    <t>عمرو محمد عبدالحليم أبو سليم</t>
-  </si>
-  <si>
     <t>اجمالي المحامين</t>
-  </si>
-  <si>
-    <t>أ/دعاء عبد الدايم إبراهيم نصار</t>
-  </si>
-  <si>
-    <t>أ/أحمد محمد رزق</t>
   </si>
   <si>
     <t>Manager Spare</t>
   </si>
   <si>
-    <t>أ/خالد محمد حلمى</t>
-  </si>
-  <si>
-    <t>أ/ نيرمين عصمت محمد حجازي</t>
-  </si>
-  <si>
     <t>Senior Spare</t>
   </si>
   <si>
-    <t>أ/مروة شريف عبدالحميد سلامة</t>
-  </si>
-  <si>
     <t>أ/حازم ابراهيم عبد الحميد محمد فتاتة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أ/أحمد سمير حسن السيد </t>
   </si>
   <si>
     <t>أ/إيمان صبحى شكرى</t>
@@ -512,6 +455,126 @@
   </si>
   <si>
     <t>تحويل/شيك</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>أ/محمد عبد العزيز عبد الحافظ محمد</t>
+  </si>
+  <si>
+    <t>أ/ احمد سعيد احمد محمد على</t>
+  </si>
+  <si>
+    <t>أ/منه الله نبيل محمد البلتاجى</t>
+  </si>
+  <si>
+    <t>أ/عبد الله عمرو عبد العزيز محمد حافظ</t>
+  </si>
+  <si>
+    <t>أ/محمد حمدى كامل مصطفى</t>
+  </si>
+  <si>
+    <t>أ/ايهاب حمدى ابراهيم امام</t>
+  </si>
+  <si>
+    <t>أ/احمد سيف الدين ابو بكر سرى الدين</t>
+  </si>
+  <si>
+    <t>أ/هانى احمد عبد المجيد مراد الدالي</t>
+  </si>
+  <si>
+    <t>أ/عبد الرحمن احمد عبد العزيز حسن</t>
+  </si>
+  <si>
+    <t>أ/حبيبه محمود سمير محمود عيسى</t>
+  </si>
+  <si>
+    <t>أ/احمد ابو العباس محمد احمد الاتربى</t>
+  </si>
+  <si>
+    <t>عمرو محمد عبد الحليم عبده سليم</t>
+  </si>
+  <si>
+    <t>2-6</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>2-9</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>2-21</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>2-8</t>
+  </si>
+  <si>
+    <t>2-7</t>
+  </si>
+  <si>
+    <t>2-16</t>
+  </si>
+  <si>
+    <t>2-14</t>
+  </si>
+  <si>
+    <t>2-17</t>
+  </si>
+  <si>
+    <t>2-20</t>
+  </si>
+  <si>
+    <t>2-22</t>
+  </si>
+  <si>
+    <t>أ/دعاء عبد الدايم ابراهيم نصار</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>أ/احمد محمد رزق محمد</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>أ/خالد محمد حلمى محمد يسرى عبد ربه</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>أ/ نرمين عصمت محمد حجازى</t>
+  </si>
+  <si>
+    <t>3-5</t>
+  </si>
+  <si>
+    <t>أ/مروة شريف عبد الحميد سلامة</t>
+  </si>
+  <si>
+    <t>3-6</t>
+  </si>
+  <si>
+    <t>3-23</t>
   </si>
 </sst>
 </file>
@@ -949,6 +1012,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1005,9 +1071,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1250,7 +1313,7 @@
       <sheetName val="Pay Clip (EN)"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="4">
           <cell r="F4">
@@ -3364,8 +3427,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3637,7 +3700,7 @@
   <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="1.109375" customWidth="1"/>
     <col min="4" max="16" width="20.77734375" customWidth="1"/>
@@ -3660,53 +3723,53 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="65" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" s="65" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="65" t="s">
-        <v>149</v>
-      </c>
-      <c r="I3" s="65" t="s">
-        <v>150</v>
-      </c>
-      <c r="J3" s="65" t="s">
-        <v>151</v>
-      </c>
-      <c r="K3" s="65" t="s">
-        <v>152</v>
-      </c>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65" t="s">
-        <v>153</v>
-      </c>
-      <c r="N3" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="O3" s="65" t="s">
-        <v>78</v>
-      </c>
-      <c r="P3" s="65" t="s">
-        <v>155</v>
+      <c r="E3" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="I3" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="J3" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="N3" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="O3" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="46" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
+      <c r="A4" t="s">
+        <v>137</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -3744,8 +3807,8 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
+      <c r="A5" t="s">
+        <v>138</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -3783,11 +3846,11 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>3</v>
+      <c r="A6" t="s">
+        <v>139</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -3823,7 +3886,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -3859,7 +3922,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -3895,7 +3958,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3931,7 +3994,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3967,7 +4030,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4003,7 +4066,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4039,7 +4102,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4075,7 +4138,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4111,7 +4174,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -4147,7 +4210,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -4183,7 +4246,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -4219,10 +4282,11 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
+        <f>COUNTA(A4:A17)</f>
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18">
         <f>SUM(D4:D17)</f>
@@ -4262,11 +4326,11 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>1</v>
+      <c r="A19" t="s">
+        <v>152</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -4301,11 +4365,11 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>2</v>
+      <c r="A20" t="s">
+        <v>153</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -4340,11 +4404,11 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>3</v>
+      <c r="A21" t="s">
+        <v>154</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4379,11 +4443,11 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>4</v>
+      <c r="A22" t="s">
+        <v>155</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4418,11 +4482,11 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>5</v>
+      <c r="A23" t="s">
+        <v>156</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -4457,11 +4521,11 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>6</v>
+      <c r="A24" t="s">
+        <v>157</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -4496,11 +4560,11 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>7</v>
+      <c r="A25" t="s">
+        <v>158</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4536,7 +4600,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4572,7 +4636,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4608,7 +4672,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -4644,7 +4708,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -4680,7 +4744,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -4716,7 +4780,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -4752,7 +4816,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -4787,11 +4851,11 @@
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>8</v>
+      <c r="A33" t="s">
+        <v>159</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -4826,11 +4890,11 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>9</v>
+      <c r="A34" t="s">
+        <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -4865,11 +4929,11 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>10</v>
+      <c r="A35" t="s">
+        <v>161</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4905,7 +4969,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -4941,7 +5005,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -4977,7 +5041,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -5013,7 +5077,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -5049,7 +5113,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -5085,7 +5149,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -5121,7 +5185,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -5157,7 +5221,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -5193,7 +5257,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -5228,11 +5292,11 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>11</v>
+      <c r="A45" t="s">
+        <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -5267,11 +5331,11 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>12</v>
+      <c r="A46" t="s">
+        <v>163</v>
       </c>
       <c r="B46" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -5306,11 +5370,11 @@
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>13</v>
+      <c r="A47" t="s">
+        <v>164</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -5345,11 +5409,11 @@
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>14</v>
+      <c r="A48" t="s">
+        <v>165</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -5384,11 +5448,8 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>15</v>
-      </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -5424,7 +5485,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -5460,7 +5521,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -5496,7 +5557,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -5532,7 +5593,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -5568,7 +5629,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -5604,7 +5665,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -5640,10 +5701,11 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>15</v>
+        <f>COUNTA(A19:A55)</f>
+        <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D56">
         <f>SUM(D19:D55)</f>
@@ -5683,11 +5745,11 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>1</v>
+      <c r="A57" t="s">
+        <v>167</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -5722,11 +5784,11 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>2</v>
+      <c r="A58" t="s">
+        <v>169</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -5762,7 +5824,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -5798,7 +5860,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -5834,7 +5896,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -5869,11 +5931,11 @@
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>3</v>
+      <c r="A62" t="s">
+        <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -5908,11 +5970,11 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>4</v>
+      <c r="A63" t="s">
+        <v>173</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -5948,7 +6010,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -5984,7 +6046,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -6020,7 +6082,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -6056,7 +6118,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -6091,11 +6153,11 @@
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>5</v>
+      <c r="A68" t="s">
+        <v>175</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -6130,11 +6192,11 @@
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>6</v>
+      <c r="A69" t="s">
+        <v>176</v>
       </c>
       <c r="B69" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -6173,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -6212,7 +6274,7 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -6251,7 +6313,7 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -6290,7 +6352,7 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -6329,7 +6391,7 @@
         <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -6368,7 +6430,7 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -6407,7 +6469,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -6446,7 +6508,7 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -6485,7 +6547,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -6524,7 +6586,7 @@
         <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -6599,7 +6661,7 @@
         <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -6638,7 +6700,7 @@
         <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -6677,7 +6739,7 @@
         <v>18</v>
       </c>
       <c r="B83" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -6716,7 +6778,7 @@
         <v>19</v>
       </c>
       <c r="B84" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -6754,9 +6816,6 @@
       <c r="A85">
         <v>20</v>
       </c>
-      <c r="B85" t="s">
-        <v>49</v>
-      </c>
       <c r="D85">
         <v>0</v>
       </c>
@@ -6791,7 +6850,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -6827,7 +6886,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -6863,7 +6922,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -6899,7 +6958,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -6935,7 +6994,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -6971,7 +7030,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -7007,7 +7066,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -7043,7 +7102,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -7079,7 +7138,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -7115,7 +7174,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -7151,7 +7210,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -7187,7 +7246,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -7223,7 +7282,7 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -7259,7 +7318,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -7295,7 +7354,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -7331,10 +7390,11 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>20</v>
+        <f>COUNTA(A57:A100)</f>
+        <v>22</v>
       </c>
       <c r="B101" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D101">
         <f>SUM(D57:D100)</f>
@@ -7378,7 +7438,7 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -7417,7 +7477,7 @@
         <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -7456,7 +7516,7 @@
         <v>3</v>
       </c>
       <c r="B104" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -7495,7 +7555,7 @@
         <v>4</v>
       </c>
       <c r="B105" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -7534,7 +7594,7 @@
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -7573,7 +7633,7 @@
         <v>6</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -7612,7 +7672,7 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -7648,7 +7708,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -7684,7 +7744,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -7720,7 +7780,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -7756,7 +7816,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -7792,7 +7852,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -7828,7 +7888,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -7864,7 +7924,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -7900,7 +7960,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -7936,7 +7996,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -7972,10 +8032,11 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>6</v>
+        <f>COUNTA(A102:A117)</f>
+        <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D118">
         <f>SUM(D102:D117)</f>
@@ -8017,10 +8078,10 @@
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119">
         <f t="shared" ref="A119" si="9">SUM(A18,A56,A101)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B119" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D119">
         <f>SUM(D18,D56,D101)</f>
@@ -8062,10 +8123,10 @@
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120">
         <f>SUM(A18,A56,A101,A118)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B120" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D120">
         <f t="shared" ref="D120:K120" si="11">SUM(D18,D56,D101,D118)</f>
@@ -8122,7 +8183,7 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B1" s="44"/>
       <c r="C1" s="44"/>
@@ -8142,62 +8203,62 @@
       <c r="Q1" s="44"/>
     </row>
     <row r="2" spans="1:17" s="43" customFormat="1" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="s">
-        <v>62</v>
+      <c r="A2" s="46" t="s">
+        <v>43</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="65" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" s="65" t="s">
-        <v>74</v>
-      </c>
-      <c r="N2" s="65" t="s">
-        <v>75</v>
-      </c>
-      <c r="O2" s="65" t="s">
-        <v>76</v>
-      </c>
-      <c r="P2" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="65" t="s">
-        <v>78</v>
+        <v>44</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="N2" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O2" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" s="46" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="44"/>
       <c r="B3" s="44" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
@@ -8216,9 +8277,9 @@
       <c r="Q3" s="44"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="44">
+      <c r="A4" s="44" t="str">
         <f>مرتبات!A4</f>
-        <v>1</v>
+        <v>1-1</v>
       </c>
       <c r="B4" s="44" t="str">
         <f>مرتبات!B4</f>
@@ -8273,9 +8334,9 @@
       <c r="Q4" s="44"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="44">
+      <c r="A5" s="44" t="str">
         <f>مرتبات!A5</f>
-        <v>2</v>
+        <v>1-2</v>
       </c>
       <c r="B5" s="44" t="str">
         <f>مرتبات!B5</f>
@@ -8330,13 +8391,13 @@
       <c r="Q5" s="44"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="44">
+      <c r="A6" s="44" t="str">
         <f>مرتبات!A6</f>
-        <v>3</v>
+        <v>2-4</v>
       </c>
       <c r="B6" s="44" t="str">
         <f>مرتبات!B6</f>
-        <v>أ/إيهاب حمدى ابراهيم</v>
+        <v>أ/ايهاب حمدى ابراهيم امام</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -9019,7 +9080,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -9038,9 +9099,9 @@
       <c r="Q18" s="44"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="44">
+      <c r="A19" s="44" t="str">
         <f>مرتبات!A19</f>
-        <v>1</v>
+        <v>2-6</v>
       </c>
       <c r="B19" s="44" t="str">
         <f>مرتبات!B19</f>
@@ -9095,13 +9156,13 @@
       <c r="Q19" s="44"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="44">
+      <c r="A20" s="44" t="str">
         <f>مرتبات!A20</f>
-        <v>2</v>
+        <v>2-1</v>
       </c>
       <c r="B20" s="44" t="str">
         <f>مرتبات!B20</f>
-        <v>أ/محمد عبد العزيز عبدالحافظ</v>
+        <v>أ/محمد عبد العزيز عبد الحافظ محمد</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -9152,13 +9213,13 @@
       <c r="Q20" s="44"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="44">
+      <c r="A21" s="44" t="str">
         <f>مرتبات!A21</f>
-        <v>3</v>
+        <v>2-9</v>
       </c>
       <c r="B21" s="44" t="str">
         <f>مرتبات!B21</f>
-        <v>أ/ أحمد سعيد أحمد محمد علي</v>
+        <v>أ/ احمد سعيد احمد محمد على</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
@@ -9209,13 +9270,13 @@
       <c r="Q21" s="44"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="44">
+      <c r="A22" s="44" t="str">
         <f>مرتبات!A22</f>
-        <v>4</v>
+        <v>2-3</v>
       </c>
       <c r="B22" s="44" t="str">
         <f>مرتبات!B22</f>
-        <v>أ/منة الله البلتاجى</v>
+        <v>أ/منه الله نبيل محمد البلتاجى</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -9266,9 +9327,9 @@
       <c r="Q22" s="44"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="44">
+      <c r="A23" s="44" t="str">
         <f>مرتبات!A23</f>
-        <v>5</v>
+        <v>2-5</v>
       </c>
       <c r="B23" s="44" t="str">
         <f>مرتبات!B23</f>
@@ -9323,13 +9384,13 @@
       <c r="Q23" s="44"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="44">
+      <c r="A24" s="44" t="str">
         <f>مرتبات!A24</f>
-        <v>6</v>
+        <v>2-21</v>
       </c>
       <c r="B24" s="44" t="str">
         <f>مرتبات!B24</f>
-        <v>أ/عبد الله عمرو حافظ</v>
+        <v>أ/عبد الله عمرو عبد العزيز محمد حافظ</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
@@ -9380,13 +9441,13 @@
       <c r="Q24" s="44"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="44">
+      <c r="A25" s="44" t="str">
         <f>مرتبات!A25</f>
-        <v>7</v>
+        <v>2-2</v>
       </c>
       <c r="B25" s="44" t="str">
         <f>مرتبات!B25</f>
-        <v>أ/محمد حمدى كامل</v>
+        <v>أ/محمد حمدى كامل مصطفى</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -9836,13 +9897,13 @@
       <c r="Q32" s="44"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="44">
+      <c r="A33" s="44" t="str">
         <f>مرتبات!A33</f>
-        <v>8</v>
+        <v>2-8</v>
       </c>
       <c r="B33" s="44" t="str">
         <f>مرتبات!B33</f>
-        <v>أ/أحمد سيف الدين أبو بكر سري الدين</v>
+        <v>أ/احمد سيف الدين ابو بكر سرى الدين</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -9893,13 +9954,13 @@
       <c r="Q33" s="44"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="44">
+      <c r="A34" s="44" t="str">
         <f>مرتبات!A34</f>
-        <v>9</v>
+        <v>2-7</v>
       </c>
       <c r="B34" s="44" t="str">
         <f>مرتبات!B34</f>
-        <v>أ/هاني أحمد الدالي</v>
+        <v>أ/هانى احمد عبد المجيد مراد الدالي</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -9950,13 +10011,13 @@
       <c r="Q34" s="44"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="44">
+      <c r="A35" s="44" t="str">
         <f>مرتبات!A35</f>
-        <v>10</v>
+        <v>2-16</v>
       </c>
       <c r="B35" s="44" t="str">
         <f>مرتبات!B35</f>
-        <v>أ/عبدالرحمن أحمد عبدالعزيز حسن</v>
+        <v>أ/عبد الرحمن احمد عبد العزيز حسن</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -10520,13 +10581,13 @@
       <c r="Q44" s="44"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="44">
+      <c r="A45" s="44" t="str">
         <f>مرتبات!A45</f>
-        <v>11</v>
+        <v>2-14</v>
       </c>
       <c r="B45" s="44" t="str">
         <f>مرتبات!B45</f>
-        <v>أ/حبيبة محمود سمير محمود عيسى</v>
+        <v>أ/حبيبه محمود سمير محمود عيسى</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -10577,13 +10638,13 @@
       <c r="Q45" s="44"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="44">
+      <c r="A46" s="44" t="str">
         <f>مرتبات!A46</f>
-        <v>12</v>
+        <v>2-17</v>
       </c>
       <c r="B46" s="44" t="str">
         <f>مرتبات!B46</f>
-        <v>أ/احمد ابو العباس محمد الاتربي</v>
+        <v>أ/احمد ابو العباس محمد احمد الاتربى</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -10634,13 +10695,13 @@
       <c r="Q46" s="44"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="44">
+      <c r="A47" s="44" t="str">
         <f>مرتبات!A47</f>
-        <v>13</v>
+        <v>2-20</v>
       </c>
       <c r="B47" s="44" t="str">
         <f>مرتبات!B47</f>
-        <v>أ/ليلي امين محمد امين طموم</v>
+        <v>أ/كريم ايمن محمد عادل</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -10691,13 +10752,13 @@
       <c r="Q47" s="44"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="44">
+      <c r="A48" s="44" t="str">
         <f>مرتبات!A48</f>
-        <v>14</v>
+        <v>2-22</v>
       </c>
       <c r="B48" s="44" t="str">
         <f>مرتبات!B48</f>
-        <v>أ/كريم ايمن محمد عادل</v>
+        <v>عمرو محمد عبد الحليم عبده سليم</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -10750,11 +10811,11 @@
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="44">
         <f>مرتبات!A49</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B49" s="44" t="str">
         <f>مرتبات!B49</f>
-        <v>عمرو محمد عبدالحليم أبو سليم</v>
+        <v>Spare</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -11149,10 +11210,10 @@
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="44">
         <f>مرتبات!A56</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B56" s="44" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -11171,13 +11232,13 @@
       <c r="Q56" s="44"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A57" s="44">
+      <c r="A57" s="44" t="str">
         <f>مرتبات!A57</f>
-        <v>1</v>
+        <v>3-1</v>
       </c>
       <c r="B57" s="44" t="str">
         <f>مرتبات!B57</f>
-        <v>أ/دعاء عبد الدايم إبراهيم نصار</v>
+        <v>أ/دعاء عبد الدايم ابراهيم نصار</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -11228,13 +11289,13 @@
       <c r="Q57" s="44"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A58" s="44">
+      <c r="A58" s="44" t="str">
         <f>مرتبات!A58</f>
-        <v>2</v>
+        <v>3-3</v>
       </c>
       <c r="B58" s="44" t="str">
         <f>مرتبات!B58</f>
-        <v>أ/أحمد محمد رزق</v>
+        <v>أ/احمد محمد رزق محمد</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -11456,13 +11517,13 @@
       <c r="Q61" s="44"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A62" s="44">
+      <c r="A62" s="44" t="str">
         <f>مرتبات!A62</f>
-        <v>3</v>
+        <v>3-2</v>
       </c>
       <c r="B62" s="44" t="str">
         <f>مرتبات!B62</f>
-        <v>أ/خالد محمد حلمى</v>
+        <v>أ/خالد محمد حلمى محمد يسرى عبد ربه</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -11513,13 +11574,13 @@
       <c r="Q62" s="44"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A63" s="44">
+      <c r="A63" s="44" t="str">
         <f>مرتبات!A63</f>
-        <v>4</v>
+        <v>3-5</v>
       </c>
       <c r="B63" s="44" t="str">
         <f>مرتبات!B63</f>
-        <v>أ/ نيرمين عصمت محمد حجازي</v>
+        <v>أ/ نرمين عصمت محمد حجازى</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -11798,13 +11859,13 @@
       <c r="Q67" s="44"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A68" s="44">
+      <c r="A68" s="44" t="str">
         <f>مرتبات!A68</f>
-        <v>5</v>
+        <v>3-6</v>
       </c>
       <c r="B68" s="44" t="str">
         <f>مرتبات!B68</f>
-        <v>أ/مروة شريف عبدالحميد سلامة</v>
+        <v>أ/مروة شريف عبد الحميد سلامة</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -11855,9 +11916,9 @@
       <c r="Q68" s="44"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A69" s="44">
+      <c r="A69" s="44" t="str">
         <f>مرتبات!A69</f>
-        <v>6</v>
+        <v>3-23</v>
       </c>
       <c r="B69" s="44" t="str">
         <f>مرتبات!B69</f>
@@ -11916,9 +11977,9 @@
         <f>مرتبات!A70</f>
         <v>0</v>
       </c>
-      <c r="B70" s="44" t="str">
-        <f>مرتبات!B70</f>
-        <v xml:space="preserve">أ/أحمد سمير حسن السيد </v>
+      <c r="B70" s="44" t="e">
+        <f>مرتبات!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -12772,7 +12833,7 @@
         <v>20</v>
       </c>
       <c r="B85" s="44" t="str">
-        <f>مرتبات!B85</f>
+        <f>مرتبات!B70</f>
         <v>محمد حسين محمد محمد</v>
       </c>
       <c r="C85" s="2">
@@ -13683,7 +13744,7 @@
         <v>19</v>
       </c>
       <c r="B101" s="44" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -14049,7 +14110,7 @@
         <v>7</v>
       </c>
       <c r="B108" s="44" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="C108" s="2">
         <v>0</v>
@@ -14615,10 +14676,10 @@
     <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="44">
         <f>مرتبات!A118</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B118" s="44" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C118" s="2">
         <f t="shared" ref="C118:L118" si="12">SUM(C4:C17)+SUM(C19:C55)+SUM(C57:C100)+SUM(C102:C117)</f>
@@ -14695,59 +14756,59 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="I2" s="65" t="s">
-        <v>93</v>
-      </c>
-      <c r="J2" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="65" t="s">
-        <v>95</v>
-      </c>
-      <c r="L2" s="65" t="s">
-        <v>96</v>
-      </c>
-      <c r="M2" s="65" t="s">
-        <v>78</v>
+      <c r="A2" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="46" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" t="str">
         <f>مرتبات!A4</f>
-        <v>1</v>
+        <v>1-1</v>
       </c>
       <c r="B4" t="str">
         <f>مرتبات!B4</f>
@@ -14786,9 +14847,9 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" t="str">
         <f>مرتبات!A5</f>
-        <v>2</v>
+        <v>1-2</v>
       </c>
       <c r="B5" t="str">
         <f>مرتبات!B5</f>
@@ -14827,13 +14888,13 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" t="str">
         <f>مرتبات!A6</f>
-        <v>3</v>
+        <v>2-4</v>
       </c>
       <c r="B6" t="str">
         <f>مرتبات!B6</f>
-        <v>أ/إيهاب حمدى ابراهيم</v>
+        <v>أ/ايهاب حمدى ابراهيم امام</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -15324,13 +15385,13 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" t="str">
         <f>مرتبات!A19</f>
-        <v>1</v>
+        <v>2-6</v>
       </c>
       <c r="B19" t="str">
         <f>مرتبات!B19</f>
@@ -15369,13 +15430,13 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" t="str">
         <f>مرتبات!A20</f>
-        <v>2</v>
+        <v>2-1</v>
       </c>
       <c r="B20" t="str">
         <f>مرتبات!B20</f>
-        <v>أ/محمد عبد العزيز عبدالحافظ</v>
+        <v>أ/محمد عبد العزيز عبد الحافظ محمد</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -15410,13 +15471,13 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" t="str">
         <f>مرتبات!A21</f>
-        <v>3</v>
+        <v>2-9</v>
       </c>
       <c r="B21" t="str">
         <f>مرتبات!B21</f>
-        <v>أ/ أحمد سعيد أحمد محمد علي</v>
+        <v>أ/ احمد سعيد احمد محمد على</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -15451,13 +15512,13 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" t="str">
         <f>مرتبات!A22</f>
-        <v>4</v>
+        <v>2-3</v>
       </c>
       <c r="B22" t="str">
         <f>مرتبات!B22</f>
-        <v>أ/منة الله البلتاجى</v>
+        <v>أ/منه الله نبيل محمد البلتاجى</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -15492,9 +15553,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" t="str">
         <f>مرتبات!A23</f>
-        <v>5</v>
+        <v>2-5</v>
       </c>
       <c r="B23" t="str">
         <f>مرتبات!B23</f>
@@ -15533,13 +15594,13 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" t="str">
         <f>مرتبات!A24</f>
-        <v>6</v>
+        <v>2-21</v>
       </c>
       <c r="B24" t="str">
         <f>مرتبات!B24</f>
-        <v>أ/عبد الله عمرو حافظ</v>
+        <v>أ/عبد الله عمرو عبد العزيز محمد حافظ</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -15574,13 +15635,13 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" t="str">
         <f>مرتبات!A25</f>
-        <v>7</v>
+        <v>2-2</v>
       </c>
       <c r="B25" t="str">
         <f>مرتبات!B25</f>
-        <v>أ/محمد حمدى كامل</v>
+        <v>أ/محمد حمدى كامل مصطفى</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -15902,13 +15963,13 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="A33" t="str">
         <f>مرتبات!A33</f>
-        <v>8</v>
+        <v>2-8</v>
       </c>
       <c r="B33" t="str">
         <f>مرتبات!B33</f>
-        <v>أ/أحمد سيف الدين أبو بكر سري الدين</v>
+        <v>أ/احمد سيف الدين ابو بكر سرى الدين</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -15943,13 +16004,13 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="A34" t="str">
         <f>مرتبات!A34</f>
-        <v>9</v>
+        <v>2-7</v>
       </c>
       <c r="B34" t="str">
         <f>مرتبات!B34</f>
-        <v>أ/هاني أحمد الدالي</v>
+        <v>أ/هانى احمد عبد المجيد مراد الدالي</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -15984,13 +16045,13 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="A35" t="str">
         <f>مرتبات!A35</f>
-        <v>10</v>
+        <v>2-16</v>
       </c>
       <c r="B35" t="str">
         <f>مرتبات!B35</f>
-        <v>أ/عبدالرحمن أحمد عبدالعزيز حسن</v>
+        <v>أ/عبد الرحمن احمد عبد العزيز حسن</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -16394,13 +16455,13 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="A45" t="str">
         <f>مرتبات!A45</f>
-        <v>11</v>
+        <v>2-14</v>
       </c>
       <c r="B45" t="str">
         <f>مرتبات!B45</f>
-        <v>أ/حبيبة محمود سمير محمود عيسى</v>
+        <v>أ/حبيبه محمود سمير محمود عيسى</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -16435,13 +16496,13 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="A46" t="str">
         <f>مرتبات!A46</f>
-        <v>12</v>
+        <v>2-17</v>
       </c>
       <c r="B46" t="str">
         <f>مرتبات!B46</f>
-        <v>أ/احمد ابو العباس محمد الاتربي</v>
+        <v>أ/احمد ابو العباس محمد احمد الاتربى</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -16476,13 +16537,13 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="A47" t="str">
         <f>مرتبات!A47</f>
-        <v>13</v>
+        <v>2-20</v>
       </c>
       <c r="B47" t="str">
         <f>مرتبات!B47</f>
-        <v>أ/ليلي امين محمد امين طموم</v>
+        <v>أ/كريم ايمن محمد عادل</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -16517,13 +16578,13 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="A48" t="str">
         <f>مرتبات!A48</f>
-        <v>14</v>
+        <v>2-22</v>
       </c>
       <c r="B48" t="str">
         <f>مرتبات!B48</f>
-        <v>أ/كريم ايمن محمد عادل</v>
+        <v>عمرو محمد عبد الحليم عبده سليم</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -16560,11 +16621,11 @@
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49">
         <f>مرتبات!A49</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B49" t="str">
         <f>مرتبات!B49</f>
-        <v>عمرو محمد عبدالحليم أبو سليم</v>
+        <v>Spare</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -16847,20 +16908,20 @@
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56">
         <f>مرتبات!A56</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57">
+      <c r="A57" t="str">
         <f>مرتبات!A57</f>
-        <v>1</v>
+        <v>3-1</v>
       </c>
       <c r="B57" t="str">
         <f>مرتبات!B57</f>
-        <v>أ/دعاء عبد الدايم إبراهيم نصار</v>
+        <v>أ/دعاء عبد الدايم ابراهيم نصار</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -16895,13 +16956,13 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58">
+      <c r="A58" t="str">
         <f>مرتبات!A58</f>
-        <v>2</v>
+        <v>3-3</v>
       </c>
       <c r="B58" t="str">
         <f>مرتبات!B58</f>
-        <v>أ/أحمد محمد رزق</v>
+        <v>أ/احمد محمد رزق محمد</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -17059,13 +17120,13 @@
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62">
+      <c r="A62" t="str">
         <f>مرتبات!A62</f>
-        <v>3</v>
+        <v>3-2</v>
       </c>
       <c r="B62" t="str">
         <f>مرتبات!B62</f>
-        <v>أ/خالد محمد حلمى</v>
+        <v>أ/خالد محمد حلمى محمد يسرى عبد ربه</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -17100,13 +17161,13 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63">
+      <c r="A63" t="str">
         <f>مرتبات!A63</f>
-        <v>4</v>
+        <v>3-5</v>
       </c>
       <c r="B63" t="str">
         <f>مرتبات!B63</f>
-        <v>أ/ نيرمين عصمت محمد حجازي</v>
+        <v>أ/ نرمين عصمت محمد حجازى</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -17305,13 +17366,13 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68">
+      <c r="A68" t="str">
         <f>مرتبات!A68</f>
-        <v>5</v>
+        <v>3-6</v>
       </c>
       <c r="B68" t="str">
         <f>مرتبات!B68</f>
-        <v>أ/مروة شريف عبدالحميد سلامة</v>
+        <v>أ/مروة شريف عبد الحميد سلامة</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -17346,9 +17407,9 @@
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69">
+      <c r="A69" t="str">
         <f>مرتبات!A69</f>
-        <v>6</v>
+        <v>3-23</v>
       </c>
       <c r="B69" t="str">
         <f>مرتبات!B69</f>
@@ -17390,9 +17451,9 @@
       <c r="A70">
         <v>0</v>
       </c>
-      <c r="B70" t="str">
-        <f>مرتبات!B70</f>
-        <v xml:space="preserve">أ/أحمد سمير حسن السيد </v>
+      <c r="B70" t="e">
+        <f>مرتبات!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -17992,7 +18053,7 @@
         <v>20</v>
       </c>
       <c r="B85" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -18646,7 +18707,7 @@
         <v>20</v>
       </c>
       <c r="B101" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -19309,7 +19370,7 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C118">
         <f>SUM(C4:C17)+SUM(C19:C55)+SUM(C57:C100)+SUM(C102:C117)</f>
@@ -19394,20 +19455,20 @@
     <row r="3" spans="1:8" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20"/>
       <c r="B3" s="25"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="54"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
       <c r="G3" s="26"/>
       <c r="H3" s="8" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20"/>
       <c r="B4" s="25"/>
       <c r="C4" s="27" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D4" s="9" t="str">
         <f>INDEX(مرتبات!B1:B1066,H4,1)</f>
@@ -19429,28 +19490,28 @@
       <c r="A5" s="20"/>
       <c r="B5" s="25"/>
       <c r="C5" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="55">
+        <v>81</v>
+      </c>
+      <c r="D5" s="56">
         <f>SUM((INDEX(مرتبات!D1:D1066,H4,1)),VALUE((INDEX(مرتبات!G1:G1066,H4,1))))</f>
         <v>0</v>
       </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="58"/>
       <c r="G5" s="26"/>
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20"/>
       <c r="B6" s="25"/>
-      <c r="C6" s="58" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="58" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="59"/>
+      <c r="C6" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="60"/>
+      <c r="E6" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="60"/>
       <c r="G6" s="26"/>
       <c r="H6" s="8"/>
     </row>
@@ -19458,14 +19519,14 @@
       <c r="A7" s="20"/>
       <c r="B7" s="25"/>
       <c r="C7" s="11" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D7" s="28">
         <f>INDEX(اضافات!C1:C1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="F7" s="29">
         <f>INDEX(خصومات!C1:C1069,H4,1)</f>
@@ -19478,14 +19539,14 @@
       <c r="A8" s="20"/>
       <c r="B8" s="25"/>
       <c r="C8" s="13" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="D8" s="28">
         <f>INDEX(اضافات!D1:D1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="F8" s="29">
         <f>INDEX(خصومات!E1:E1070,H4,1)</f>
@@ -19498,14 +19559,14 @@
       <c r="A9" s="20"/>
       <c r="B9" s="25"/>
       <c r="C9" s="14" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D9" s="28">
         <f>INDEX(اضافات!E1:E1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="F9" s="29">
         <f>INDEX(خصومات!F1:F1071,H4,1)</f>
@@ -19518,14 +19579,14 @@
       <c r="A10" s="20"/>
       <c r="B10" s="25"/>
       <c r="C10" s="14" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="D10" s="28">
         <f>INDEX(اضافات!L1:L1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="F10" s="29">
         <f>INDEX(خصومات!I1:I1072,H4,1)</f>
@@ -19538,14 +19599,14 @@
       <c r="A11" s="20"/>
       <c r="B11" s="25"/>
       <c r="C11" s="14" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="D11" s="28">
         <f>INDEX(اضافات!J1:J1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="F11" s="29">
         <f>INDEX(خصومات!H1:H1073,H4,1)</f>
@@ -19558,14 +19619,14 @@
       <c r="A12" s="20"/>
       <c r="B12" s="25"/>
       <c r="C12" s="14" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="D12" s="28">
         <f>INDEX(اضافات!I1:I1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="F12" s="29">
         <f>INDEX(خصومات!D1:D1074,H4,1)</f>
@@ -19578,14 +19639,14 @@
       <c r="A13" s="20"/>
       <c r="B13" s="25"/>
       <c r="C13" s="14" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D13" s="28">
         <f>INDEX(اضافات!K1:K1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="F13" s="29">
         <f>INDEX(خصومات!G1:G1075,H4,1)</f>
@@ -19600,7 +19661,7 @@
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="F14" s="29">
         <f>INDEX(خصومات!J1:J1076,H4,1)</f>
@@ -19615,7 +19676,7 @@
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="14" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="F15" s="29">
         <f>INDEX(خصومات!K1:K1077,H4,1)</f>
@@ -19628,14 +19689,14 @@
       <c r="A16" s="20"/>
       <c r="B16" s="25"/>
       <c r="C16" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D16" s="55">
+        <v>100</v>
+      </c>
+      <c r="D16" s="56">
         <f>D5+D7+D8+D9+D10+D11+D12+D13</f>
         <v>0</v>
       </c>
-      <c r="E16" s="56"/>
-      <c r="F16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="58"/>
       <c r="G16" s="26"/>
       <c r="H16" s="8"/>
     </row>
@@ -19643,14 +19704,14 @@
       <c r="A17" s="20"/>
       <c r="B17" s="25"/>
       <c r="C17" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="55">
+        <v>101</v>
+      </c>
+      <c r="D17" s="56">
         <f>SUM(D7:D15)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="56"/>
-      <c r="F17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="58"/>
       <c r="G17" s="26"/>
       <c r="H17" s="8"/>
     </row>
@@ -19658,14 +19719,14 @@
       <c r="A18" s="20"/>
       <c r="B18" s="25"/>
       <c r="C18" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="46">
+        <v>102</v>
+      </c>
+      <c r="D18" s="47">
         <f>(SUM(F7:F15))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="49"/>
       <c r="G18" s="26"/>
       <c r="H18" s="8"/>
     </row>
@@ -19673,14 +19734,14 @@
       <c r="A19" s="20"/>
       <c r="B19" s="25"/>
       <c r="C19" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" s="49">
+        <v>103</v>
+      </c>
+      <c r="D19" s="50">
         <f>D16-D17-D18</f>
         <v>0</v>
       </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="52"/>
       <c r="G19" s="26"/>
       <c r="H19" s="8"/>
     </row>
@@ -19738,26 +19799,26 @@
     </row>
     <row r="3" spans="2:8" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="6"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="54"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
       <c r="G3" s="7"/>
       <c r="H3" s="8" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="6"/>
       <c r="C4" s="33" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D4" s="34" t="str">
         <f>INDEX(مرتبات!B1:B1066,H4,1)</f>
         <v>أ/ناجى رمضان أمين محمد</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="F4" s="34">
         <f>مرتبات!D2</f>
@@ -19771,41 +19832,41 @@
     <row r="5" spans="2:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="6"/>
       <c r="C5" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="60">
+        <v>106</v>
+      </c>
+      <c r="D5" s="61">
         <f>SUM((INDEX(مرتبات!D1:D1066,H4,1)),VALUE((INDEX(مرتبات!G1:G1066,H4,1))))</f>
         <v>0</v>
       </c>
-      <c r="E5" s="61"/>
-      <c r="F5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="63"/>
       <c r="G5" s="7"/>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
-      <c r="C6" s="63" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="58" t="s">
-        <v>127</v>
-      </c>
-      <c r="F6" s="59"/>
+      <c r="C6" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="65"/>
+      <c r="E6" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="60"/>
       <c r="G6" s="7"/>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6"/>
       <c r="C7" s="36" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D7" s="12">
         <f>INDEX(اضافات!C1:C1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="F7" s="37">
         <f>INDEX(خصومات!C1:C1069,H4,1)</f>
@@ -19817,14 +19878,14 @@
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="6"/>
       <c r="C8" s="38" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="D8" s="12">
         <f>INDEX(اضافات!D1:D1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="F8" s="37">
         <f>INDEX(خصومات!E1:E1070,H4,1)</f>
@@ -19836,14 +19897,14 @@
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="6"/>
       <c r="C9" s="39" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D9" s="12">
         <f>INDEX(اضافات!E1:E1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="F9" s="37">
         <f>INDEX(خصومات!F1:F1071,H4,1)</f>
@@ -19855,14 +19916,14 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
       <c r="C10" s="39" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D10" s="12">
         <f>INDEX(اضافات!L1:L1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="F10" s="37">
         <f>INDEX(خصومات!I1:I1072,H4,1)</f>
@@ -19874,14 +19935,14 @@
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="6"/>
       <c r="C11" s="39" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D11" s="12">
         <f>INDEX(اضافات!J1:J1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F11" s="37">
         <f>INDEX(خصومات!H1:H1073,H4,1)</f>
@@ -19893,14 +19954,14 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6"/>
       <c r="C12" s="39" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D12" s="12">
         <f>INDEX(اضافات!I1:I1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="F12" s="37">
         <f>INDEX(خصومات!D1:D1074,H4,1)</f>
@@ -19912,14 +19973,14 @@
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6"/>
       <c r="C13" s="39" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="D13" s="12">
         <f>INDEX(اضافات!K1:K1069,H4,1)</f>
         <v>0</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="F13" s="37">
         <f>INDEX(خصومات!G1:G1075,H4,1)</f>
@@ -19933,7 +19994,7 @@
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="39" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="F14" s="37">
         <f>INDEX(خصومات!J1:J1076,H4,1)</f>
@@ -19947,7 +20008,7 @@
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="39" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="F15" s="37">
         <f>INDEX(خصومات!K1:K1077,H4,1)</f>
@@ -19959,56 +20020,56 @@
     <row r="16" spans="2:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="6"/>
       <c r="C16" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" s="60">
+        <v>125</v>
+      </c>
+      <c r="D16" s="61">
         <f>D5+D7+D8+D9+D10+D11+D12+D13</f>
         <v>0</v>
       </c>
-      <c r="E16" s="61"/>
-      <c r="F16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="63"/>
       <c r="G16" s="7"/>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="2:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="6"/>
       <c r="C17" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="46">
+        <v>126</v>
+      </c>
+      <c r="D17" s="47">
         <f>SUM(D7:D15)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="49"/>
       <c r="G17" s="7"/>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="2:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="6"/>
       <c r="C18" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="46">
+        <v>108</v>
+      </c>
+      <c r="D18" s="47">
         <f>(SUM(F7:F15))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="49"/>
       <c r="G18" s="7"/>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="2:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="6"/>
       <c r="C19" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="49">
+        <v>127</v>
+      </c>
+      <c r="D19" s="50">
         <f>D16-D17-D18</f>
         <v>0</v>
       </c>
-      <c r="E19" s="50"/>
-      <c r="F19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="52"/>
       <c r="G19" s="7"/>
       <c r="H19" s="2"/>
     </row>
